--- a/backend/templates/Resumen_1ro_2do.xlsx
+++ b/backend/templates/Resumen_1ro_2do.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JavierWorkSpace\BatallaProject\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71919519-009D-461F-925B-CD0C44398B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6445754-FCC8-461B-97D0-ED95D0BCB9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{299BAFB4-AE58-4015-B36E-D7CD92F1B4DD}"/>
+    <workbookView xWindow="-21555" yWindow="1080" windowWidth="20070" windowHeight="17205" xr2:uid="{299BAFB4-AE58-4015-B36E-D7CD92F1B4DD}"/>
   </bookViews>
   <sheets>
     <sheet name="1er Año" sheetId="5" r:id="rId1"/>
@@ -2173,28 +2173,293 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2202,23 +2467,95 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
@@ -2226,357 +2563,149 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2593,35 +2722,20 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -2632,125 +2746,11 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3142,116 +3142,116 @@
   <sheetData>
     <row r="1" spans="1:28" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H1" s="9"/>
-      <c r="N1" s="51" t="s">
+      <c r="N1" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
     </row>
     <row r="2" spans="1:28" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63"/>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="N2" s="43" t="s">
+      <c r="A2" s="47"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="N2" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="48"/>
+      <c r="Y2" s="48"/>
     </row>
     <row r="3" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="64" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="64"/>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-      <c r="W3" s="56"/>
-      <c r="X3" s="56"/>
-      <c r="Y3" s="56"/>
-      <c r="Z3" s="56"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="50"/>
+      <c r="W3" s="50"/>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="50"/>
+      <c r="Z3" s="50"/>
     </row>
     <row r="4" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="64" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="66"/>
-      <c r="O4" s="66"/>
-      <c r="P4" s="66"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="66"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="66"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="65" t="s">
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="51" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
       <c r="Z4" s="10"/>
     </row>
     <row r="5" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="63"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -3272,12 +3272,12 @@
       <c r="Z5" s="5"/>
     </row>
     <row r="6" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -3308,28 +3308,28 @@
       <c r="B7" s="54"/>
       <c r="C7" s="54"/>
       <c r="D7" s="54"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="61" t="s">
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="61"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="62"/>
-      <c r="L7" s="62"/>
-      <c r="M7" s="62"/>
-      <c r="N7" s="62"/>
-      <c r="O7" s="62"/>
-      <c r="P7" s="62"/>
-      <c r="Q7" s="62"/>
-      <c r="R7" s="62"/>
-      <c r="S7" s="62"/>
-      <c r="T7" s="62"/>
-      <c r="U7" s="62"/>
-      <c r="V7" s="62"/>
-      <c r="W7" s="62"/>
-      <c r="X7" s="62"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="56"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
@@ -3338,227 +3338,227 @@
         <v>90</v>
       </c>
       <c r="B8" s="54"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="55" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="50"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="50"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="50"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="50"/>
+      <c r="R8" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-      <c r="W8" s="56"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="56"/>
-      <c r="Z8" s="56"/>
+      <c r="S8" s="57"/>
+      <c r="T8" s="57"/>
+      <c r="U8" s="50"/>
+      <c r="V8" s="50"/>
+      <c r="W8" s="50"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="50"/>
+      <c r="Z8" s="50"/>
     </row>
     <row r="9" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="54" t="s">
         <v>89</v>
       </c>
       <c r="B9" s="54"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
       <c r="F9" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="55" t="s">
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="57" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
-      <c r="M9" s="55"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
-      <c r="S9" s="56"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
+      <c r="J9" s="57"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="57"/>
+      <c r="M9" s="57"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="50"/>
+      <c r="P9" s="50"/>
+      <c r="Q9" s="50"/>
+      <c r="R9" s="50"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
+      <c r="V9" s="57"/>
+      <c r="W9" s="57"/>
+      <c r="X9" s="57"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
     </row>
     <row r="10" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="224" t="s">
+      <c r="A10" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="224"/>
-      <c r="C10" s="224"/>
-      <c r="D10" s="224"/>
-      <c r="E10" s="224"/>
-      <c r="F10" s="224"/>
-      <c r="G10" s="224"/>
-      <c r="H10" s="224"/>
-      <c r="I10" s="225" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="225"/>
-      <c r="K10" s="225"/>
-      <c r="L10" s="225"/>
-      <c r="M10" s="225"/>
-      <c r="N10" s="224"/>
-      <c r="O10" s="224"/>
-      <c r="P10" s="224"/>
-      <c r="Q10" s="224"/>
-      <c r="R10" s="224"/>
-      <c r="S10" s="224"/>
-      <c r="T10" s="224"/>
-      <c r="U10" s="224"/>
-      <c r="V10" s="224"/>
-      <c r="W10" s="224"/>
-      <c r="X10" s="224"/>
-      <c r="Y10" s="224"/>
-      <c r="Z10" s="224"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="55"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="54"/>
+      <c r="S10" s="54"/>
+      <c r="T10" s="54"/>
+      <c r="U10" s="54"/>
+      <c r="V10" s="54"/>
+      <c r="W10" s="54"/>
+      <c r="X10" s="54"/>
+      <c r="Y10" s="54"/>
+      <c r="Z10" s="54"/>
     </row>
     <row r="11" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="226" t="s">
+      <c r="A11" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="227"/>
-      <c r="C11" s="227"/>
-      <c r="D11" s="227"/>
-      <c r="E11" s="227"/>
-      <c r="F11" s="227"/>
-      <c r="G11" s="227"/>
-      <c r="H11" s="227"/>
-      <c r="I11" s="227"/>
-      <c r="J11" s="227"/>
-      <c r="K11" s="227"/>
-      <c r="L11" s="227"/>
-      <c r="M11" s="228"/>
-      <c r="N11" s="227" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="60"/>
+      <c r="N11" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="O11" s="227"/>
-      <c r="P11" s="227"/>
-      <c r="Q11" s="227"/>
-      <c r="R11" s="227"/>
-      <c r="S11" s="227"/>
-      <c r="T11" s="227"/>
-      <c r="U11" s="227"/>
-      <c r="V11" s="227"/>
-      <c r="W11" s="227"/>
-      <c r="X11" s="227"/>
-      <c r="Y11" s="227"/>
-      <c r="Z11" s="228"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59"/>
+      <c r="R11" s="59"/>
+      <c r="S11" s="59"/>
+      <c r="T11" s="59"/>
+      <c r="U11" s="59"/>
+      <c r="V11" s="59"/>
+      <c r="W11" s="59"/>
+      <c r="X11" s="59"/>
+      <c r="Y11" s="59"/>
+      <c r="Z11" s="60"/>
     </row>
     <row r="12" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="187" t="s">
+      <c r="A12" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="188" t="s">
+      <c r="B12" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="189"/>
-      <c r="D12" s="190" t="s">
+      <c r="C12" s="79"/>
+      <c r="D12" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="191"/>
-      <c r="F12" s="190" t="s">
+      <c r="E12" s="85"/>
+      <c r="F12" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="191"/>
-      <c r="H12" s="212" t="s">
+      <c r="G12" s="85"/>
+      <c r="H12" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="187" t="s">
+      <c r="I12" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="192" t="s">
+      <c r="J12" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="193" t="s">
+      <c r="K12" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="194"/>
-      <c r="M12" s="218"/>
-      <c r="N12" s="135" t="s">
+      <c r="L12" s="66"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="O12" s="135"/>
-      <c r="P12" s="135"/>
-      <c r="Q12" s="135"/>
-      <c r="R12" s="135"/>
-      <c r="S12" s="135"/>
-      <c r="T12" s="135"/>
-      <c r="U12" s="135"/>
-      <c r="V12" s="135"/>
-      <c r="W12" s="170" t="s">
+      <c r="O12" s="117"/>
+      <c r="P12" s="117"/>
+      <c r="Q12" s="117"/>
+      <c r="R12" s="117"/>
+      <c r="S12" s="117"/>
+      <c r="T12" s="117"/>
+      <c r="U12" s="117"/>
+      <c r="V12" s="117"/>
+      <c r="W12" s="215" t="s">
         <v>50</v>
       </c>
-      <c r="X12" s="171"/>
-      <c r="Y12" s="171"/>
-      <c r="Z12" s="172"/>
+      <c r="X12" s="216"/>
+      <c r="Y12" s="216"/>
+      <c r="Z12" s="217"/>
     </row>
     <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="195"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="213"/>
-      <c r="I13" s="195"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="31" t="s">
+      <c r="A13" s="76"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="76"/>
+      <c r="J13" s="63"/>
+      <c r="K13" s="68"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="70"/>
+      <c r="N13" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="173"/>
-      <c r="X13" s="174"/>
-      <c r="Y13" s="174"/>
-      <c r="Z13" s="175"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="120"/>
+      <c r="Q13" s="120"/>
+      <c r="R13" s="120"/>
+      <c r="S13" s="120"/>
+      <c r="T13" s="120"/>
+      <c r="U13" s="120"/>
+      <c r="V13" s="120"/>
+      <c r="W13" s="218"/>
+      <c r="X13" s="219"/>
+      <c r="Y13" s="219"/>
+      <c r="Z13" s="220"/>
     </row>
     <row r="14" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="195"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="213"/>
-      <c r="I14" s="195"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="60" t="s">
+      <c r="A14" s="76"/>
+      <c r="B14" s="80"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="86"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="87"/>
+      <c r="H14" s="91"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="63"/>
+      <c r="K14" s="71" t="s">
         <v>42</v>
       </c>
-      <c r="L14" s="60" t="s">
+      <c r="L14" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="220" t="s">
+      <c r="M14" s="73" t="s">
         <v>44</v>
       </c>
       <c r="N14" s="16" t="s">
@@ -3588,77 +3588,77 @@
       <c r="V14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="W14" s="173"/>
-      <c r="X14" s="174"/>
-      <c r="Y14" s="174"/>
-      <c r="Z14" s="175"/>
+      <c r="W14" s="218"/>
+      <c r="X14" s="219"/>
+      <c r="Y14" s="219"/>
+      <c r="Z14" s="220"/>
     </row>
     <row r="15" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="196"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="198"/>
-      <c r="D15" s="199"/>
-      <c r="E15" s="200"/>
-      <c r="F15" s="199"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="214"/>
-      <c r="I15" s="196"/>
-      <c r="J15" s="201"/>
-      <c r="K15" s="202"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="221"/>
-      <c r="N15" s="217" t="s">
-        <v>104</v>
-      </c>
-      <c r="O15" s="203" t="s">
-        <v>104</v>
-      </c>
-      <c r="P15" s="203" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q15" s="203" t="s">
-        <v>104</v>
-      </c>
-      <c r="R15" s="203" t="s">
-        <v>104</v>
-      </c>
-      <c r="S15" s="203" t="s">
-        <v>104</v>
-      </c>
-      <c r="T15" s="204" t="s">
-        <v>104</v>
-      </c>
-      <c r="U15" s="203" t="s">
-        <v>104</v>
-      </c>
-      <c r="V15" s="205" t="s">
-        <v>104</v>
-      </c>
-      <c r="W15" s="206"/>
-      <c r="X15" s="207"/>
-      <c r="Y15" s="207"/>
-      <c r="Z15" s="208"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="64"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="O15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="S15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="T15" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="U15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="V15" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="W15" s="221"/>
+      <c r="X15" s="222"/>
+      <c r="Y15" s="222"/>
+      <c r="Z15" s="223"/>
     </row>
     <row r="16" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="209" t="s">
+      <c r="A16" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="180" t="s">
+      <c r="B16" s="97" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="181"/>
-      <c r="D16" s="182" t="s">
+      <c r="C16" s="98"/>
+      <c r="D16" s="99" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="183"/>
-      <c r="F16" s="182" t="s">
+      <c r="E16" s="100"/>
+      <c r="F16" s="99" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="183"/>
-      <c r="H16" s="215" t="s">
+      <c r="G16" s="100"/>
+      <c r="H16" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="I16" s="222" t="s">
+      <c r="I16" s="44" t="s">
         <v>104</v>
       </c>
       <c r="J16" s="19" t="s">
@@ -3670,7 +3670,7 @@
       <c r="L16" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="223" t="s">
+      <c r="M16" s="45" t="s">
         <v>104</v>
       </c>
       <c r="N16" s="23" t="s">
@@ -3700,34 +3700,34 @@
       <c r="V16" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="W16" s="184" t="s">
+      <c r="W16" s="224" t="s">
         <v>105</v>
       </c>
-      <c r="X16" s="185"/>
-      <c r="Y16" s="185"/>
-      <c r="Z16" s="186"/>
+      <c r="X16" s="225"/>
+      <c r="Y16" s="225"/>
+      <c r="Z16" s="226"/>
       <c r="AB16" s="6"/>
     </row>
     <row r="17" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="210" t="s">
+      <c r="A17" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="38" t="s">
+      <c r="C17" s="94"/>
+      <c r="D17" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="38" t="s">
+      <c r="E17" s="96"/>
+      <c r="F17" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="40"/>
+      <c r="G17" s="96"/>
       <c r="H17" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="87" t="s">
+      <c r="I17" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -3739,7 +3739,7 @@
       <c r="L17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M17" s="158" t="s">
+      <c r="M17" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N17" s="14" t="s">
@@ -3769,34 +3769,34 @@
       <c r="V17" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W17" s="176" t="s">
+      <c r="W17" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X17" s="39"/>
-      <c r="Y17" s="39"/>
-      <c r="Z17" s="88"/>
+      <c r="X17" s="102"/>
+      <c r="Y17" s="102"/>
+      <c r="Z17" s="103"/>
       <c r="AC17" s="7"/>
     </row>
     <row r="18" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="210" t="s">
+      <c r="A18" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="38" t="s">
+      <c r="C18" s="94"/>
+      <c r="D18" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="38" t="s">
+      <c r="E18" s="96"/>
+      <c r="F18" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="40"/>
+      <c r="G18" s="96"/>
       <c r="H18" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I18" s="87" t="s">
+      <c r="I18" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -3808,7 +3808,7 @@
       <c r="L18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M18" s="158" t="s">
+      <c r="M18" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N18" s="14" t="s">
@@ -3838,33 +3838,33 @@
       <c r="V18" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W18" s="176" t="s">
+      <c r="W18" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X18" s="39"/>
-      <c r="Y18" s="39"/>
-      <c r="Z18" s="88"/>
+      <c r="X18" s="102"/>
+      <c r="Y18" s="102"/>
+      <c r="Z18" s="103"/>
     </row>
     <row r="19" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="210" t="s">
+      <c r="A19" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="38" t="s">
+      <c r="C19" s="94"/>
+      <c r="D19" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="38" t="s">
+      <c r="E19" s="96"/>
+      <c r="F19" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="40"/>
+      <c r="G19" s="96"/>
       <c r="H19" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="87" t="s">
+      <c r="I19" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J19" s="4" t="s">
@@ -3876,7 +3876,7 @@
       <c r="L19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="158" t="s">
+      <c r="M19" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N19" s="14" t="s">
@@ -3906,33 +3906,33 @@
       <c r="V19" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W19" s="176" t="s">
+      <c r="W19" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X19" s="39"/>
-      <c r="Y19" s="39"/>
-      <c r="Z19" s="88"/>
+      <c r="X19" s="102"/>
+      <c r="Y19" s="102"/>
+      <c r="Z19" s="103"/>
     </row>
     <row r="20" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="210" t="s">
+      <c r="A20" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B20" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="53"/>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="94"/>
+      <c r="D20" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="38" t="s">
+      <c r="E20" s="96"/>
+      <c r="F20" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="40"/>
+      <c r="G20" s="96"/>
       <c r="H20" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="87" t="s">
+      <c r="I20" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -3944,7 +3944,7 @@
       <c r="L20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="158" t="s">
+      <c r="M20" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N20" s="14" t="s">
@@ -3974,33 +3974,33 @@
       <c r="V20" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W20" s="176" t="s">
+      <c r="W20" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="88"/>
+      <c r="X20" s="102"/>
+      <c r="Y20" s="102"/>
+      <c r="Z20" s="103"/>
     </row>
     <row r="21" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="210" t="s">
+      <c r="A21" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="38" t="s">
+      <c r="C21" s="94"/>
+      <c r="D21" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="38" t="s">
+      <c r="E21" s="96"/>
+      <c r="F21" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="40"/>
+      <c r="G21" s="96"/>
       <c r="H21" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I21" s="87" t="s">
+      <c r="I21" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J21" s="4" t="s">
@@ -4012,7 +4012,7 @@
       <c r="L21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M21" s="158" t="s">
+      <c r="M21" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N21" s="14" t="s">
@@ -4042,33 +4042,33 @@
       <c r="V21" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W21" s="176" t="s">
+      <c r="W21" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X21" s="39"/>
-      <c r="Y21" s="39"/>
-      <c r="Z21" s="88"/>
+      <c r="X21" s="102"/>
+      <c r="Y21" s="102"/>
+      <c r="Z21" s="103"/>
     </row>
     <row r="22" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="210" t="s">
+      <c r="A22" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B22" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="38" t="s">
+      <c r="C22" s="94"/>
+      <c r="D22" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="38" t="s">
+      <c r="E22" s="96"/>
+      <c r="F22" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="40"/>
+      <c r="G22" s="96"/>
       <c r="H22" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="87" t="s">
+      <c r="I22" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J22" s="4" t="s">
@@ -4080,7 +4080,7 @@
       <c r="L22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M22" s="158" t="s">
+      <c r="M22" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N22" s="14" t="s">
@@ -4110,33 +4110,33 @@
       <c r="V22" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W22" s="176" t="s">
+      <c r="W22" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X22" s="39"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="88"/>
+      <c r="X22" s="102"/>
+      <c r="Y22" s="102"/>
+      <c r="Z22" s="103"/>
     </row>
     <row r="23" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="210" t="s">
+      <c r="A23" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="52" t="s">
+      <c r="B23" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="38" t="s">
+      <c r="C23" s="94"/>
+      <c r="D23" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="38" t="s">
+      <c r="E23" s="96"/>
+      <c r="F23" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="40"/>
+      <c r="G23" s="96"/>
       <c r="H23" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="87" t="s">
+      <c r="I23" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -4148,7 +4148,7 @@
       <c r="L23" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="158" t="s">
+      <c r="M23" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N23" s="14" t="s">
@@ -4178,33 +4178,33 @@
       <c r="V23" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W23" s="176" t="s">
+      <c r="W23" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="88"/>
+      <c r="X23" s="102"/>
+      <c r="Y23" s="102"/>
+      <c r="Z23" s="103"/>
     </row>
     <row r="24" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="210" t="s">
+      <c r="A24" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="53"/>
-      <c r="D24" s="38" t="s">
+      <c r="C24" s="94"/>
+      <c r="D24" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="38" t="s">
+      <c r="E24" s="96"/>
+      <c r="F24" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="40"/>
+      <c r="G24" s="96"/>
       <c r="H24" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="87" t="s">
+      <c r="I24" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -4216,7 +4216,7 @@
       <c r="L24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M24" s="158" t="s">
+      <c r="M24" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N24" s="14" t="s">
@@ -4246,33 +4246,33 @@
       <c r="V24" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W24" s="176" t="s">
+      <c r="W24" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X24" s="39"/>
-      <c r="Y24" s="39"/>
-      <c r="Z24" s="88"/>
+      <c r="X24" s="102"/>
+      <c r="Y24" s="102"/>
+      <c r="Z24" s="103"/>
     </row>
     <row r="25" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="210" t="s">
+      <c r="A25" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="53"/>
-      <c r="D25" s="38" t="s">
+      <c r="C25" s="94"/>
+      <c r="D25" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="38" t="s">
+      <c r="E25" s="96"/>
+      <c r="F25" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="40"/>
+      <c r="G25" s="96"/>
       <c r="H25" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I25" s="87" t="s">
+      <c r="I25" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J25" s="4" t="s">
@@ -4284,7 +4284,7 @@
       <c r="L25" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M25" s="158" t="s">
+      <c r="M25" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N25" s="14" t="s">
@@ -4314,33 +4314,33 @@
       <c r="V25" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W25" s="176" t="s">
+      <c r="W25" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X25" s="39"/>
-      <c r="Y25" s="39"/>
-      <c r="Z25" s="88"/>
+      <c r="X25" s="102"/>
+      <c r="Y25" s="102"/>
+      <c r="Z25" s="103"/>
     </row>
     <row r="26" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="210" t="s">
+      <c r="A26" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="53"/>
-      <c r="D26" s="38" t="s">
+      <c r="C26" s="94"/>
+      <c r="D26" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="40"/>
-      <c r="F26" s="38" t="s">
+      <c r="E26" s="96"/>
+      <c r="F26" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="40"/>
+      <c r="G26" s="96"/>
       <c r="H26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="87" t="s">
+      <c r="I26" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J26" s="4" t="s">
@@ -4352,7 +4352,7 @@
       <c r="L26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M26" s="158" t="s">
+      <c r="M26" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N26" s="14" t="s">
@@ -4382,33 +4382,33 @@
       <c r="V26" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W26" s="176" t="s">
+      <c r="W26" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X26" s="39"/>
-      <c r="Y26" s="39"/>
-      <c r="Z26" s="88"/>
+      <c r="X26" s="102"/>
+      <c r="Y26" s="102"/>
+      <c r="Z26" s="103"/>
     </row>
     <row r="27" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="210" t="s">
+      <c r="A27" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="52" t="s">
+      <c r="B27" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="53"/>
-      <c r="D27" s="38" t="s">
+      <c r="C27" s="94"/>
+      <c r="D27" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="38" t="s">
+      <c r="E27" s="96"/>
+      <c r="F27" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="40"/>
+      <c r="G27" s="96"/>
       <c r="H27" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I27" s="87" t="s">
+      <c r="I27" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -4420,7 +4420,7 @@
       <c r="L27" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M27" s="158" t="s">
+      <c r="M27" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N27" s="14" t="s">
@@ -4450,33 +4450,33 @@
       <c r="V27" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W27" s="176" t="s">
+      <c r="W27" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X27" s="39"/>
-      <c r="Y27" s="39"/>
-      <c r="Z27" s="88"/>
+      <c r="X27" s="102"/>
+      <c r="Y27" s="102"/>
+      <c r="Z27" s="103"/>
     </row>
     <row r="28" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="210" t="s">
+      <c r="A28" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="52" t="s">
+      <c r="B28" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="53"/>
-      <c r="D28" s="38" t="s">
+      <c r="C28" s="94"/>
+      <c r="D28" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="38" t="s">
+      <c r="E28" s="96"/>
+      <c r="F28" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="40"/>
+      <c r="G28" s="96"/>
       <c r="H28" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I28" s="87" t="s">
+      <c r="I28" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J28" s="4" t="s">
@@ -4488,7 +4488,7 @@
       <c r="L28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M28" s="158" t="s">
+      <c r="M28" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N28" s="14" t="s">
@@ -4518,33 +4518,33 @@
       <c r="V28" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W28" s="176" t="s">
+      <c r="W28" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X28" s="39"/>
-      <c r="Y28" s="39"/>
-      <c r="Z28" s="88"/>
+      <c r="X28" s="102"/>
+      <c r="Y28" s="102"/>
+      <c r="Z28" s="103"/>
     </row>
     <row r="29" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="210" t="s">
+      <c r="A29" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="52" t="s">
+      <c r="B29" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="53"/>
-      <c r="D29" s="38" t="s">
+      <c r="C29" s="94"/>
+      <c r="D29" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="40"/>
-      <c r="F29" s="38" t="s">
+      <c r="E29" s="96"/>
+      <c r="F29" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="40"/>
+      <c r="G29" s="96"/>
       <c r="H29" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I29" s="87" t="s">
+      <c r="I29" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J29" s="4" t="s">
@@ -4556,7 +4556,7 @@
       <c r="L29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M29" s="158" t="s">
+      <c r="M29" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N29" s="14" t="s">
@@ -4586,33 +4586,33 @@
       <c r="V29" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W29" s="176" t="s">
+      <c r="W29" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="39"/>
-      <c r="Z29" s="88"/>
+      <c r="X29" s="102"/>
+      <c r="Y29" s="102"/>
+      <c r="Z29" s="103"/>
     </row>
     <row r="30" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="210" t="s">
+      <c r="A30" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="52" t="s">
+      <c r="B30" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="38" t="s">
+      <c r="C30" s="94"/>
+      <c r="D30" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="40"/>
-      <c r="F30" s="38" t="s">
+      <c r="E30" s="96"/>
+      <c r="F30" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G30" s="40"/>
+      <c r="G30" s="96"/>
       <c r="H30" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I30" s="87" t="s">
+      <c r="I30" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J30" s="4" t="s">
@@ -4624,7 +4624,7 @@
       <c r="L30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M30" s="158" t="s">
+      <c r="M30" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N30" s="14" t="s">
@@ -4654,33 +4654,33 @@
       <c r="V30" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W30" s="176" t="s">
+      <c r="W30" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X30" s="39"/>
-      <c r="Y30" s="39"/>
-      <c r="Z30" s="88"/>
+      <c r="X30" s="102"/>
+      <c r="Y30" s="102"/>
+      <c r="Z30" s="103"/>
     </row>
     <row r="31" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="210" t="s">
+      <c r="A31" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="52" t="s">
+      <c r="B31" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="53"/>
-      <c r="D31" s="38" t="s">
+      <c r="C31" s="94"/>
+      <c r="D31" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="40"/>
-      <c r="F31" s="38" t="s">
+      <c r="E31" s="96"/>
+      <c r="F31" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="40"/>
+      <c r="G31" s="96"/>
       <c r="H31" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="87" t="s">
+      <c r="I31" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -4692,7 +4692,7 @@
       <c r="L31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M31" s="158" t="s">
+      <c r="M31" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N31" s="14" t="s">
@@ -4722,33 +4722,33 @@
       <c r="V31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W31" s="176" t="s">
+      <c r="W31" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X31" s="39"/>
-      <c r="Y31" s="39"/>
-      <c r="Z31" s="88"/>
+      <c r="X31" s="102"/>
+      <c r="Y31" s="102"/>
+      <c r="Z31" s="103"/>
     </row>
     <row r="32" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="210" t="s">
+      <c r="A32" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="52" t="s">
+      <c r="B32" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="38" t="s">
+      <c r="C32" s="94"/>
+      <c r="D32" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="38" t="s">
+      <c r="E32" s="96"/>
+      <c r="F32" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="40"/>
+      <c r="G32" s="96"/>
       <c r="H32" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="87" t="s">
+      <c r="I32" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -4760,7 +4760,7 @@
       <c r="L32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M32" s="158" t="s">
+      <c r="M32" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N32" s="14" t="s">
@@ -4790,33 +4790,33 @@
       <c r="V32" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W32" s="176" t="s">
+      <c r="W32" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X32" s="39"/>
-      <c r="Y32" s="39"/>
-      <c r="Z32" s="88"/>
+      <c r="X32" s="102"/>
+      <c r="Y32" s="102"/>
+      <c r="Z32" s="103"/>
     </row>
     <row r="33" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="210" t="s">
+      <c r="A33" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="53"/>
-      <c r="D33" s="38" t="s">
+      <c r="C33" s="94"/>
+      <c r="D33" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="38" t="s">
+      <c r="E33" s="96"/>
+      <c r="F33" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G33" s="40"/>
+      <c r="G33" s="96"/>
       <c r="H33" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I33" s="87" t="s">
+      <c r="I33" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J33" s="4" t="s">
@@ -4828,7 +4828,7 @@
       <c r="L33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M33" s="158" t="s">
+      <c r="M33" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N33" s="14" t="s">
@@ -4858,33 +4858,33 @@
       <c r="V33" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W33" s="176" t="s">
+      <c r="W33" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X33" s="39"/>
-      <c r="Y33" s="39"/>
-      <c r="Z33" s="88"/>
+      <c r="X33" s="102"/>
+      <c r="Y33" s="102"/>
+      <c r="Z33" s="103"/>
     </row>
     <row r="34" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="210" t="s">
+      <c r="A34" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="52" t="s">
+      <c r="B34" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="53"/>
-      <c r="D34" s="38" t="s">
+      <c r="C34" s="94"/>
+      <c r="D34" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="40"/>
-      <c r="F34" s="38" t="s">
+      <c r="E34" s="96"/>
+      <c r="F34" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G34" s="40"/>
+      <c r="G34" s="96"/>
       <c r="H34" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I34" s="87" t="s">
+      <c r="I34" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J34" s="4" t="s">
@@ -4896,7 +4896,7 @@
       <c r="L34" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M34" s="158" t="s">
+      <c r="M34" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N34" s="14" t="s">
@@ -4926,33 +4926,33 @@
       <c r="V34" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W34" s="176" t="s">
+      <c r="W34" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X34" s="39"/>
-      <c r="Y34" s="39"/>
-      <c r="Z34" s="88"/>
+      <c r="X34" s="102"/>
+      <c r="Y34" s="102"/>
+      <c r="Z34" s="103"/>
     </row>
     <row r="35" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="210" t="s">
+      <c r="A35" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="52" t="s">
+      <c r="B35" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="53"/>
-      <c r="D35" s="38" t="s">
+      <c r="C35" s="94"/>
+      <c r="D35" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="40"/>
-      <c r="F35" s="38" t="s">
+      <c r="E35" s="96"/>
+      <c r="F35" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="40"/>
+      <c r="G35" s="96"/>
       <c r="H35" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I35" s="87" t="s">
+      <c r="I35" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J35" s="4" t="s">
@@ -4964,7 +4964,7 @@
       <c r="L35" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M35" s="158" t="s">
+      <c r="M35" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N35" s="14" t="s">
@@ -4994,33 +4994,33 @@
       <c r="V35" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W35" s="176" t="s">
+      <c r="W35" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X35" s="39"/>
-      <c r="Y35" s="39"/>
-      <c r="Z35" s="88"/>
+      <c r="X35" s="102"/>
+      <c r="Y35" s="102"/>
+      <c r="Z35" s="103"/>
     </row>
     <row r="36" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="210" t="s">
+      <c r="A36" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="52" t="s">
+      <c r="B36" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="53"/>
-      <c r="D36" s="38" t="s">
+      <c r="C36" s="94"/>
+      <c r="D36" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="40"/>
-      <c r="F36" s="38" t="s">
+      <c r="E36" s="96"/>
+      <c r="F36" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="40"/>
+      <c r="G36" s="96"/>
       <c r="H36" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I36" s="87" t="s">
+      <c r="I36" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J36" s="4" t="s">
@@ -5032,7 +5032,7 @@
       <c r="L36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M36" s="158" t="s">
+      <c r="M36" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N36" s="14" t="s">
@@ -5062,33 +5062,33 @@
       <c r="V36" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W36" s="176" t="s">
+      <c r="W36" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X36" s="39"/>
-      <c r="Y36" s="39"/>
-      <c r="Z36" s="88"/>
+      <c r="X36" s="102"/>
+      <c r="Y36" s="102"/>
+      <c r="Z36" s="103"/>
     </row>
     <row r="37" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="210" t="s">
+      <c r="A37" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="52" t="s">
+      <c r="B37" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="53"/>
-      <c r="D37" s="38" t="s">
+      <c r="C37" s="94"/>
+      <c r="D37" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="40"/>
-      <c r="F37" s="38" t="s">
+      <c r="E37" s="96"/>
+      <c r="F37" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="40"/>
+      <c r="G37" s="96"/>
       <c r="H37" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I37" s="87" t="s">
+      <c r="I37" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J37" s="4" t="s">
@@ -5100,7 +5100,7 @@
       <c r="L37" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M37" s="158" t="s">
+      <c r="M37" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N37" s="14" t="s">
@@ -5130,33 +5130,33 @@
       <c r="V37" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W37" s="176" t="s">
+      <c r="W37" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X37" s="39"/>
-      <c r="Y37" s="39"/>
-      <c r="Z37" s="88"/>
+      <c r="X37" s="102"/>
+      <c r="Y37" s="102"/>
+      <c r="Z37" s="103"/>
     </row>
     <row r="38" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="210" t="s">
+      <c r="A38" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="52" t="s">
+      <c r="B38" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="53"/>
-      <c r="D38" s="38" t="s">
+      <c r="C38" s="94"/>
+      <c r="D38" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="40"/>
-      <c r="F38" s="38" t="s">
+      <c r="E38" s="96"/>
+      <c r="F38" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="40"/>
+      <c r="G38" s="96"/>
       <c r="H38" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I38" s="87" t="s">
+      <c r="I38" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J38" s="4" t="s">
@@ -5168,7 +5168,7 @@
       <c r="L38" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M38" s="158" t="s">
+      <c r="M38" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N38" s="14" t="s">
@@ -5198,33 +5198,33 @@
       <c r="V38" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W38" s="176" t="s">
+      <c r="W38" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X38" s="39"/>
-      <c r="Y38" s="39"/>
-      <c r="Z38" s="88"/>
+      <c r="X38" s="102"/>
+      <c r="Y38" s="102"/>
+      <c r="Z38" s="103"/>
     </row>
     <row r="39" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="210" t="s">
+      <c r="A39" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="52" t="s">
+      <c r="B39" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="53"/>
-      <c r="D39" s="38" t="s">
+      <c r="C39" s="94"/>
+      <c r="D39" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="40"/>
-      <c r="F39" s="38" t="s">
+      <c r="E39" s="96"/>
+      <c r="F39" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="40"/>
+      <c r="G39" s="96"/>
       <c r="H39" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I39" s="87" t="s">
+      <c r="I39" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -5236,7 +5236,7 @@
       <c r="L39" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M39" s="158" t="s">
+      <c r="M39" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N39" s="14" t="s">
@@ -5266,33 +5266,33 @@
       <c r="V39" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W39" s="176" t="s">
+      <c r="W39" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X39" s="39"/>
-      <c r="Y39" s="39"/>
-      <c r="Z39" s="88"/>
+      <c r="X39" s="102"/>
+      <c r="Y39" s="102"/>
+      <c r="Z39" s="103"/>
     </row>
     <row r="40" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="210" t="s">
+      <c r="A40" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="52" t="s">
+      <c r="B40" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="53"/>
-      <c r="D40" s="38" t="s">
+      <c r="C40" s="94"/>
+      <c r="D40" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E40" s="40"/>
-      <c r="F40" s="38" t="s">
+      <c r="E40" s="96"/>
+      <c r="F40" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="40"/>
+      <c r="G40" s="96"/>
       <c r="H40" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I40" s="87" t="s">
+      <c r="I40" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J40" s="4" t="s">
@@ -5304,7 +5304,7 @@
       <c r="L40" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M40" s="158" t="s">
+      <c r="M40" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N40" s="14" t="s">
@@ -5334,33 +5334,33 @@
       <c r="V40" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W40" s="176" t="s">
+      <c r="W40" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X40" s="39"/>
-      <c r="Y40" s="39"/>
-      <c r="Z40" s="88"/>
+      <c r="X40" s="102"/>
+      <c r="Y40" s="102"/>
+      <c r="Z40" s="103"/>
     </row>
     <row r="41" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="210" t="s">
+      <c r="A41" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="52" t="s">
+      <c r="B41" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="53"/>
-      <c r="D41" s="38" t="s">
+      <c r="C41" s="94"/>
+      <c r="D41" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="40"/>
-      <c r="F41" s="38" t="s">
+      <c r="E41" s="96"/>
+      <c r="F41" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="40"/>
+      <c r="G41" s="96"/>
       <c r="H41" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I41" s="87" t="s">
+      <c r="I41" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J41" s="4" t="s">
@@ -5372,7 +5372,7 @@
       <c r="L41" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M41" s="158" t="s">
+      <c r="M41" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N41" s="14" t="s">
@@ -5402,33 +5402,33 @@
       <c r="V41" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W41" s="176" t="s">
+      <c r="W41" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X41" s="39"/>
-      <c r="Y41" s="39"/>
-      <c r="Z41" s="88"/>
+      <c r="X41" s="102"/>
+      <c r="Y41" s="102"/>
+      <c r="Z41" s="103"/>
     </row>
     <row r="42" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="210" t="s">
+      <c r="A42" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="52" t="s">
+      <c r="B42" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="53"/>
-      <c r="D42" s="38" t="s">
+      <c r="C42" s="94"/>
+      <c r="D42" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="40"/>
-      <c r="F42" s="38" t="s">
+      <c r="E42" s="96"/>
+      <c r="F42" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="40"/>
+      <c r="G42" s="96"/>
       <c r="H42" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I42" s="87" t="s">
+      <c r="I42" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -5440,7 +5440,7 @@
       <c r="L42" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M42" s="158" t="s">
+      <c r="M42" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N42" s="14" t="s">
@@ -5470,33 +5470,33 @@
       <c r="V42" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W42" s="176" t="s">
+      <c r="W42" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X42" s="39"/>
-      <c r="Y42" s="39"/>
-      <c r="Z42" s="88"/>
+      <c r="X42" s="102"/>
+      <c r="Y42" s="102"/>
+      <c r="Z42" s="103"/>
     </row>
     <row r="43" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="210" t="s">
+      <c r="A43" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="52" t="s">
+      <c r="B43" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="53"/>
-      <c r="D43" s="38" t="s">
+      <c r="C43" s="94"/>
+      <c r="D43" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="40"/>
-      <c r="F43" s="38" t="s">
+      <c r="E43" s="96"/>
+      <c r="F43" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G43" s="40"/>
+      <c r="G43" s="96"/>
       <c r="H43" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I43" s="87" t="s">
+      <c r="I43" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -5508,7 +5508,7 @@
       <c r="L43" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M43" s="158" t="s">
+      <c r="M43" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N43" s="14" t="s">
@@ -5538,33 +5538,33 @@
       <c r="V43" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W43" s="176" t="s">
+      <c r="W43" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X43" s="39"/>
-      <c r="Y43" s="39"/>
-      <c r="Z43" s="88"/>
+      <c r="X43" s="102"/>
+      <c r="Y43" s="102"/>
+      <c r="Z43" s="103"/>
     </row>
     <row r="44" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="210" t="s">
+      <c r="A44" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="52" t="s">
+      <c r="B44" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="53"/>
-      <c r="D44" s="38" t="s">
+      <c r="C44" s="94"/>
+      <c r="D44" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="40"/>
-      <c r="F44" s="38" t="s">
+      <c r="E44" s="96"/>
+      <c r="F44" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="40"/>
+      <c r="G44" s="96"/>
       <c r="H44" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I44" s="87" t="s">
+      <c r="I44" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J44" s="4" t="s">
@@ -5576,7 +5576,7 @@
       <c r="L44" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M44" s="158" t="s">
+      <c r="M44" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N44" s="14" t="s">
@@ -5606,33 +5606,33 @@
       <c r="V44" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W44" s="176" t="s">
+      <c r="W44" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X44" s="39"/>
-      <c r="Y44" s="39"/>
-      <c r="Z44" s="88"/>
+      <c r="X44" s="102"/>
+      <c r="Y44" s="102"/>
+      <c r="Z44" s="103"/>
     </row>
     <row r="45" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="210" t="s">
+      <c r="A45" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="52" t="s">
+      <c r="B45" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="53"/>
-      <c r="D45" s="38" t="s">
+      <c r="C45" s="94"/>
+      <c r="D45" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="40"/>
-      <c r="F45" s="38" t="s">
+      <c r="E45" s="96"/>
+      <c r="F45" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G45" s="40"/>
+      <c r="G45" s="96"/>
       <c r="H45" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I45" s="87" t="s">
+      <c r="I45" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J45" s="4" t="s">
@@ -5644,7 +5644,7 @@
       <c r="L45" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M45" s="158" t="s">
+      <c r="M45" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N45" s="14" t="s">
@@ -5674,33 +5674,33 @@
       <c r="V45" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W45" s="176" t="s">
+      <c r="W45" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X45" s="39"/>
-      <c r="Y45" s="39"/>
-      <c r="Z45" s="88"/>
+      <c r="X45" s="102"/>
+      <c r="Y45" s="102"/>
+      <c r="Z45" s="103"/>
     </row>
     <row r="46" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="210" t="s">
+      <c r="A46" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="52" t="s">
+      <c r="B46" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="53"/>
-      <c r="D46" s="38" t="s">
+      <c r="C46" s="94"/>
+      <c r="D46" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="40"/>
-      <c r="F46" s="38" t="s">
+      <c r="E46" s="96"/>
+      <c r="F46" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G46" s="40"/>
+      <c r="G46" s="96"/>
       <c r="H46" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I46" s="87" t="s">
+      <c r="I46" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J46" s="4" t="s">
@@ -5712,7 +5712,7 @@
       <c r="L46" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M46" s="158" t="s">
+      <c r="M46" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N46" s="14" t="s">
@@ -5742,33 +5742,33 @@
       <c r="V46" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W46" s="176" t="s">
+      <c r="W46" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X46" s="39"/>
-      <c r="Y46" s="39"/>
-      <c r="Z46" s="88"/>
+      <c r="X46" s="102"/>
+      <c r="Y46" s="102"/>
+      <c r="Z46" s="103"/>
     </row>
     <row r="47" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="210" t="s">
+      <c r="A47" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="52" t="s">
+      <c r="B47" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="53"/>
-      <c r="D47" s="38" t="s">
+      <c r="C47" s="94"/>
+      <c r="D47" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="40"/>
-      <c r="F47" s="38" t="s">
+      <c r="E47" s="96"/>
+      <c r="F47" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G47" s="40"/>
+      <c r="G47" s="96"/>
       <c r="H47" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I47" s="87" t="s">
+      <c r="I47" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J47" s="4" t="s">
@@ -5780,7 +5780,7 @@
       <c r="L47" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M47" s="158" t="s">
+      <c r="M47" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N47" s="14" t="s">
@@ -5810,33 +5810,33 @@
       <c r="V47" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W47" s="176" t="s">
+      <c r="W47" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X47" s="39"/>
-      <c r="Y47" s="39"/>
-      <c r="Z47" s="88"/>
+      <c r="X47" s="102"/>
+      <c r="Y47" s="102"/>
+      <c r="Z47" s="103"/>
     </row>
     <row r="48" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="210" t="s">
+      <c r="A48" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="52" t="s">
+      <c r="B48" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="53"/>
-      <c r="D48" s="38" t="s">
+      <c r="C48" s="94"/>
+      <c r="D48" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="40"/>
-      <c r="F48" s="38" t="s">
+      <c r="E48" s="96"/>
+      <c r="F48" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G48" s="40"/>
+      <c r="G48" s="96"/>
       <c r="H48" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I48" s="87" t="s">
+      <c r="I48" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J48" s="4" t="s">
@@ -5848,7 +5848,7 @@
       <c r="L48" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M48" s="158" t="s">
+      <c r="M48" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N48" s="14" t="s">
@@ -5878,33 +5878,33 @@
       <c r="V48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W48" s="176" t="s">
+      <c r="W48" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X48" s="39"/>
-      <c r="Y48" s="39"/>
-      <c r="Z48" s="88"/>
+      <c r="X48" s="102"/>
+      <c r="Y48" s="102"/>
+      <c r="Z48" s="103"/>
     </row>
     <row r="49" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="210" t="s">
+      <c r="A49" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="52" t="s">
+      <c r="B49" s="93" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="53"/>
-      <c r="D49" s="38" t="s">
+      <c r="C49" s="94"/>
+      <c r="D49" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="E49" s="40"/>
-      <c r="F49" s="38" t="s">
+      <c r="E49" s="96"/>
+      <c r="F49" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="G49" s="40"/>
+      <c r="G49" s="96"/>
       <c r="H49" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I49" s="87" t="s">
+      <c r="I49" s="27" t="s">
         <v>104</v>
       </c>
       <c r="J49" s="4" t="s">
@@ -5916,7 +5916,7 @@
       <c r="L49" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M49" s="158" t="s">
+      <c r="M49" s="32" t="s">
         <v>104</v>
       </c>
       <c r="N49" s="14" t="s">
@@ -5946,45 +5946,45 @@
       <c r="V49" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W49" s="176" t="s">
+      <c r="W49" s="101" t="s">
         <v>105</v>
       </c>
-      <c r="X49" s="39"/>
-      <c r="Y49" s="39"/>
-      <c r="Z49" s="88"/>
+      <c r="X49" s="102"/>
+      <c r="Y49" s="102"/>
+      <c r="Z49" s="103"/>
     </row>
     <row r="50" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="211" t="s">
+      <c r="A50" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="72" t="s">
+      <c r="B50" s="104" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="73"/>
-      <c r="D50" s="74" t="s">
+      <c r="C50" s="105"/>
+      <c r="D50" s="106" t="s">
         <v>101</v>
       </c>
-      <c r="E50" s="75"/>
-      <c r="F50" s="74" t="s">
+      <c r="E50" s="107"/>
+      <c r="F50" s="106" t="s">
         <v>102</v>
       </c>
-      <c r="G50" s="75"/>
-      <c r="H50" s="216" t="s">
+      <c r="G50" s="107"/>
+      <c r="H50" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="I50" s="159" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="K50" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="L50" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="M50" s="161" t="s">
+      <c r="I50" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="K50" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="M50" s="35" t="s">
         <v>104</v>
       </c>
       <c r="N50" s="21" t="s">
@@ -6014,80 +6014,80 @@
       <c r="V50" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="W50" s="177" t="s">
+      <c r="W50" s="203" t="s">
         <v>105</v>
       </c>
-      <c r="X50" s="178"/>
-      <c r="Y50" s="178"/>
-      <c r="Z50" s="179"/>
+      <c r="X50" s="204"/>
+      <c r="Y50" s="204"/>
+      <c r="Z50" s="205"/>
     </row>
     <row r="51" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="76" t="s">
+      <c r="A51" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="77"/>
-      <c r="C51" s="77"/>
-      <c r="D51" s="77"/>
-      <c r="E51" s="78"/>
-      <c r="F51" s="134" t="s">
+      <c r="B51" s="109"/>
+      <c r="C51" s="109"/>
+      <c r="D51" s="109"/>
+      <c r="E51" s="110"/>
+      <c r="F51" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="G51" s="135"/>
-      <c r="H51" s="135"/>
-      <c r="I51" s="135"/>
-      <c r="J51" s="135"/>
-      <c r="K51" s="135"/>
-      <c r="L51" s="135"/>
-      <c r="M51" s="136"/>
-      <c r="N51" s="155" t="s">
-        <v>104</v>
-      </c>
-      <c r="O51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="R51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="S51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="T51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="U51" s="156" t="s">
-        <v>104</v>
-      </c>
-      <c r="V51" s="157" t="s">
-        <v>104</v>
-      </c>
-      <c r="W51" s="162"/>
-      <c r="X51" s="163"/>
-      <c r="Y51" s="163"/>
-      <c r="Z51" s="164"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="117"/>
+      <c r="I51" s="117"/>
+      <c r="J51" s="117"/>
+      <c r="K51" s="117"/>
+      <c r="L51" s="117"/>
+      <c r="M51" s="118"/>
+      <c r="N51" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="O51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="S51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="T51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="U51" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="V51" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="W51" s="206"/>
+      <c r="X51" s="207"/>
+      <c r="Y51" s="207"/>
+      <c r="Z51" s="208"/>
     </row>
     <row r="52" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="79"/>
-      <c r="B52" s="80"/>
-      <c r="C52" s="80"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="137" t="s">
+      <c r="A52" s="111"/>
+      <c r="B52" s="112"/>
+      <c r="C52" s="112"/>
+      <c r="D52" s="112"/>
+      <c r="E52" s="113"/>
+      <c r="F52" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="31"/>
-      <c r="K52" s="31"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="138"/>
-      <c r="N52" s="87" t="s">
+      <c r="G52" s="120"/>
+      <c r="H52" s="120"/>
+      <c r="I52" s="120"/>
+      <c r="J52" s="120"/>
+      <c r="K52" s="120"/>
+      <c r="L52" s="120"/>
+      <c r="M52" s="121"/>
+      <c r="N52" s="27" t="s">
         <v>104</v>
       </c>
       <c r="O52" s="4" t="s">
@@ -6111,31 +6111,31 @@
       <c r="U52" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="V52" s="158" t="s">
-        <v>104</v>
-      </c>
-      <c r="W52" s="165"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="166"/>
+      <c r="V52" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="W52" s="209"/>
+      <c r="X52" s="210"/>
+      <c r="Y52" s="210"/>
+      <c r="Z52" s="211"/>
     </row>
     <row r="53" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="79"/>
-      <c r="B53" s="80"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="137" t="s">
+      <c r="A53" s="111"/>
+      <c r="B53" s="112"/>
+      <c r="C53" s="112"/>
+      <c r="D53" s="112"/>
+      <c r="E53" s="113"/>
+      <c r="F53" s="119" t="s">
         <v>63</v>
       </c>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="138"/>
-      <c r="N53" s="87" t="s">
+      <c r="G53" s="120"/>
+      <c r="H53" s="120"/>
+      <c r="I53" s="120"/>
+      <c r="J53" s="120"/>
+      <c r="K53" s="120"/>
+      <c r="L53" s="120"/>
+      <c r="M53" s="121"/>
+      <c r="N53" s="27" t="s">
         <v>104</v>
       </c>
       <c r="O53" s="4" t="s">
@@ -6159,31 +6159,31 @@
       <c r="U53" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="V53" s="158" t="s">
-        <v>104</v>
-      </c>
-      <c r="W53" s="165"/>
-      <c r="X53" s="27"/>
-      <c r="Y53" s="27"/>
-      <c r="Z53" s="166"/>
+      <c r="V53" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="W53" s="209"/>
+      <c r="X53" s="210"/>
+      <c r="Y53" s="210"/>
+      <c r="Z53" s="211"/>
     </row>
     <row r="54" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="79"/>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="81"/>
-      <c r="F54" s="137" t="s">
+      <c r="A54" s="111"/>
+      <c r="B54" s="112"/>
+      <c r="C54" s="112"/>
+      <c r="D54" s="112"/>
+      <c r="E54" s="113"/>
+      <c r="F54" s="119" t="s">
         <v>64</v>
       </c>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="31"/>
-      <c r="K54" s="31"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="138"/>
-      <c r="N54" s="87" t="s">
+      <c r="G54" s="120"/>
+      <c r="H54" s="120"/>
+      <c r="I54" s="120"/>
+      <c r="J54" s="120"/>
+      <c r="K54" s="120"/>
+      <c r="L54" s="120"/>
+      <c r="M54" s="121"/>
+      <c r="N54" s="27" t="s">
         <v>104</v>
       </c>
       <c r="O54" s="4" t="s">
@@ -6207,1005 +6207,798 @@
       <c r="U54" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="V54" s="158" t="s">
-        <v>104</v>
-      </c>
-      <c r="W54" s="165"/>
-      <c r="X54" s="27"/>
-      <c r="Y54" s="27"/>
-      <c r="Z54" s="166"/>
+      <c r="V54" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="W54" s="209"/>
+      <c r="X54" s="210"/>
+      <c r="Y54" s="210"/>
+      <c r="Z54" s="211"/>
     </row>
     <row r="55" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="82"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="83"/>
-      <c r="F55" s="152" t="s">
+      <c r="A55" s="114"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="115"/>
+      <c r="F55" s="133" t="s">
         <v>65</v>
       </c>
-      <c r="G55" s="153"/>
-      <c r="H55" s="153"/>
-      <c r="I55" s="153"/>
-      <c r="J55" s="153"/>
-      <c r="K55" s="153"/>
-      <c r="L55" s="153"/>
-      <c r="M55" s="154"/>
-      <c r="N55" s="159" t="s">
-        <v>104</v>
-      </c>
-      <c r="O55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="P55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="R55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="S55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="T55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="U55" s="160" t="s">
-        <v>104</v>
-      </c>
-      <c r="V55" s="161" t="s">
-        <v>104</v>
-      </c>
-      <c r="W55" s="167"/>
-      <c r="X55" s="168"/>
-      <c r="Y55" s="168"/>
-      <c r="Z55" s="169"/>
+      <c r="G55" s="134"/>
+      <c r="H55" s="134"/>
+      <c r="I55" s="134"/>
+      <c r="J55" s="134"/>
+      <c r="K55" s="134"/>
+      <c r="L55" s="134"/>
+      <c r="M55" s="135"/>
+      <c r="N55" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="O55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="P55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="R55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="S55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="T55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="U55" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="V55" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="W55" s="212"/>
+      <c r="X55" s="213"/>
+      <c r="Y55" s="213"/>
+      <c r="Z55" s="214"/>
     </row>
     <row r="56" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="84" t="s">
+      <c r="A56" s="136" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="99" t="s">
+      <c r="B56" s="123"/>
+      <c r="C56" s="123"/>
+      <c r="D56" s="123"/>
+      <c r="E56" s="124"/>
+      <c r="F56" s="137" t="s">
         <v>75</v>
       </c>
-      <c r="G56" s="100"/>
-      <c r="H56" s="101" t="s">
+      <c r="G56" s="138"/>
+      <c r="H56" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="I56" s="102" t="s">
+      <c r="I56" s="143" t="s">
         <v>76</v>
       </c>
-      <c r="J56" s="103"/>
-      <c r="K56" s="103"/>
-      <c r="L56" s="103"/>
-      <c r="M56" s="103"/>
-      <c r="N56" s="103"/>
-      <c r="O56" s="104"/>
-      <c r="P56" s="134" t="s">
+      <c r="J56" s="144"/>
+      <c r="K56" s="144"/>
+      <c r="L56" s="144"/>
+      <c r="M56" s="144"/>
+      <c r="N56" s="144"/>
+      <c r="O56" s="145"/>
+      <c r="P56" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="Q56" s="135"/>
-      <c r="R56" s="135"/>
-      <c r="S56" s="135"/>
-      <c r="T56" s="135"/>
-      <c r="U56" s="135"/>
-      <c r="V56" s="135"/>
-      <c r="W56" s="135"/>
-      <c r="X56" s="135"/>
-      <c r="Y56" s="135"/>
-      <c r="Z56" s="136"/>
+      <c r="Q56" s="117"/>
+      <c r="R56" s="117"/>
+      <c r="S56" s="117"/>
+      <c r="T56" s="117"/>
+      <c r="U56" s="117"/>
+      <c r="V56" s="117"/>
+      <c r="W56" s="117"/>
+      <c r="X56" s="117"/>
+      <c r="Y56" s="117"/>
+      <c r="Z56" s="118"/>
     </row>
     <row r="57" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="47"/>
-      <c r="K57" s="47"/>
-      <c r="L57" s="47"/>
-      <c r="M57" s="47"/>
-      <c r="N57" s="47"/>
-      <c r="O57" s="106"/>
-      <c r="P57" s="137" t="s">
+      <c r="C57" s="123"/>
+      <c r="D57" s="123"/>
+      <c r="E57" s="124"/>
+      <c r="F57" s="139"/>
+      <c r="G57" s="140"/>
+      <c r="H57" s="142"/>
+      <c r="I57" s="146"/>
+      <c r="J57" s="147"/>
+      <c r="K57" s="147"/>
+      <c r="L57" s="147"/>
+      <c r="M57" s="147"/>
+      <c r="N57" s="147"/>
+      <c r="O57" s="148"/>
+      <c r="P57" s="119" t="s">
         <v>78</v>
       </c>
-      <c r="Q57" s="31"/>
-      <c r="R57" s="31"/>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="31"/>
-      <c r="W57" s="31"/>
-      <c r="X57" s="31"/>
-      <c r="Y57" s="31"/>
-      <c r="Z57" s="138"/>
+      <c r="Q57" s="120"/>
+      <c r="R57" s="120"/>
+      <c r="S57" s="120"/>
+      <c r="T57" s="120"/>
+      <c r="U57" s="120"/>
+      <c r="V57" s="120"/>
+      <c r="W57" s="120"/>
+      <c r="X57" s="120"/>
+      <c r="Y57" s="120"/>
+      <c r="Z57" s="121"/>
     </row>
     <row r="58" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="38" t="s">
+      <c r="C58" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="39"/>
-      <c r="E58" s="88"/>
-      <c r="F58" s="107" t="s">
+      <c r="D58" s="102"/>
+      <c r="E58" s="103"/>
+      <c r="F58" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G58" s="69"/>
-      <c r="H58" s="68" t="s">
+      <c r="G58" s="126"/>
+      <c r="H58" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I58" s="48" t="s">
+      <c r="I58" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J58" s="70"/>
-      <c r="K58" s="70"/>
-      <c r="L58" s="70"/>
-      <c r="M58" s="70"/>
-      <c r="N58" s="70"/>
-      <c r="O58" s="108"/>
-      <c r="P58" s="139"/>
-      <c r="Q58" s="25"/>
-      <c r="R58" s="25"/>
-      <c r="S58" s="25"/>
-      <c r="T58" s="25"/>
-      <c r="U58" s="25"/>
-      <c r="V58" s="25"/>
-      <c r="W58" s="25"/>
-      <c r="X58" s="25"/>
-      <c r="Y58" s="25"/>
-      <c r="Z58" s="140"/>
+      <c r="J58" s="128"/>
+      <c r="K58" s="128"/>
+      <c r="L58" s="128"/>
+      <c r="M58" s="128"/>
+      <c r="N58" s="128"/>
+      <c r="O58" s="129"/>
+      <c r="P58" s="130"/>
+      <c r="Q58" s="131"/>
+      <c r="R58" s="131"/>
+      <c r="S58" s="131"/>
+      <c r="T58" s="131"/>
+      <c r="U58" s="131"/>
+      <c r="V58" s="131"/>
+      <c r="W58" s="131"/>
+      <c r="X58" s="131"/>
+      <c r="Y58" s="131"/>
+      <c r="Z58" s="132"/>
     </row>
     <row r="59" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="87" t="s">
+      <c r="A59" s="27" t="s">
         <v>1</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="38" t="s">
+      <c r="C59" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="39"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="107" t="s">
+      <c r="D59" s="102"/>
+      <c r="E59" s="103"/>
+      <c r="F59" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G59" s="69"/>
-      <c r="H59" s="68" t="s">
+      <c r="G59" s="126"/>
+      <c r="H59" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I59" s="48" t="s">
+      <c r="I59" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J59" s="70"/>
-      <c r="K59" s="70"/>
-      <c r="L59" s="70"/>
-      <c r="M59" s="70"/>
-      <c r="N59" s="70"/>
-      <c r="O59" s="108"/>
-      <c r="P59" s="137" t="s">
+      <c r="J59" s="128"/>
+      <c r="K59" s="128"/>
+      <c r="L59" s="128"/>
+      <c r="M59" s="128"/>
+      <c r="N59" s="128"/>
+      <c r="O59" s="129"/>
+      <c r="P59" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="Q59" s="31"/>
-      <c r="R59" s="31"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="31"/>
-      <c r="W59" s="31"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
-      <c r="Z59" s="138"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="120"/>
+      <c r="S59" s="120"/>
+      <c r="T59" s="120"/>
+      <c r="U59" s="120"/>
+      <c r="V59" s="120"/>
+      <c r="W59" s="120"/>
+      <c r="X59" s="120"/>
+      <c r="Y59" s="120"/>
+      <c r="Z59" s="121"/>
     </row>
     <row r="60" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="87" t="s">
+      <c r="A60" s="27" t="s">
         <v>2</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="38" t="s">
+      <c r="C60" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D60" s="39"/>
-      <c r="E60" s="88"/>
-      <c r="F60" s="107" t="s">
+      <c r="D60" s="102"/>
+      <c r="E60" s="103"/>
+      <c r="F60" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G60" s="69"/>
-      <c r="H60" s="68" t="s">
+      <c r="G60" s="126"/>
+      <c r="H60" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I60" s="48" t="s">
+      <c r="I60" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J60" s="70"/>
-      <c r="K60" s="70"/>
-      <c r="L60" s="70"/>
-      <c r="M60" s="70"/>
-      <c r="N60" s="70"/>
-      <c r="O60" s="108"/>
-      <c r="P60" s="137"/>
-      <c r="Q60" s="31"/>
-      <c r="R60" s="31"/>
-      <c r="S60" s="31"/>
-      <c r="T60" s="31"/>
-      <c r="U60" s="31"/>
-      <c r="V60" s="31"/>
-      <c r="W60" s="31"/>
-      <c r="X60" s="31"/>
-      <c r="Y60" s="31"/>
-      <c r="Z60" s="138"/>
+      <c r="J60" s="128"/>
+      <c r="K60" s="128"/>
+      <c r="L60" s="128"/>
+      <c r="M60" s="128"/>
+      <c r="N60" s="128"/>
+      <c r="O60" s="129"/>
+      <c r="P60" s="119"/>
+      <c r="Q60" s="120"/>
+      <c r="R60" s="120"/>
+      <c r="S60" s="120"/>
+      <c r="T60" s="120"/>
+      <c r="U60" s="120"/>
+      <c r="V60" s="120"/>
+      <c r="W60" s="120"/>
+      <c r="X60" s="120"/>
+      <c r="Y60" s="120"/>
+      <c r="Z60" s="121"/>
     </row>
     <row r="61" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="87" t="s">
+      <c r="A61" s="27" t="s">
         <v>3</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C61" s="38" t="s">
+      <c r="C61" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D61" s="39"/>
-      <c r="E61" s="88"/>
-      <c r="F61" s="107" t="s">
+      <c r="D61" s="102"/>
+      <c r="E61" s="103"/>
+      <c r="F61" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G61" s="69"/>
-      <c r="H61" s="68" t="s">
+      <c r="G61" s="126"/>
+      <c r="H61" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I61" s="48" t="s">
+      <c r="I61" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J61" s="70"/>
-      <c r="K61" s="70"/>
-      <c r="L61" s="70"/>
-      <c r="M61" s="70"/>
-      <c r="N61" s="70"/>
-      <c r="O61" s="108"/>
-      <c r="P61" s="137" t="s">
+      <c r="J61" s="128"/>
+      <c r="K61" s="128"/>
+      <c r="L61" s="128"/>
+      <c r="M61" s="128"/>
+      <c r="N61" s="128"/>
+      <c r="O61" s="129"/>
+      <c r="P61" s="119" t="s">
         <v>80</v>
       </c>
-      <c r="Q61" s="31"/>
-      <c r="R61" s="31"/>
-      <c r="S61" s="31"/>
-      <c r="T61" s="31"/>
-      <c r="U61" s="31"/>
-      <c r="V61" s="31"/>
-      <c r="W61" s="31"/>
-      <c r="X61" s="31"/>
-      <c r="Y61" s="31"/>
-      <c r="Z61" s="138"/>
+      <c r="Q61" s="120"/>
+      <c r="R61" s="120"/>
+      <c r="S61" s="120"/>
+      <c r="T61" s="120"/>
+      <c r="U61" s="120"/>
+      <c r="V61" s="120"/>
+      <c r="W61" s="120"/>
+      <c r="X61" s="120"/>
+      <c r="Y61" s="120"/>
+      <c r="Z61" s="121"/>
     </row>
     <row r="62" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="27" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C62" s="38" t="s">
+      <c r="C62" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D62" s="39"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="107" t="s">
+      <c r="D62" s="102"/>
+      <c r="E62" s="103"/>
+      <c r="F62" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G62" s="69"/>
-      <c r="H62" s="68" t="s">
+      <c r="G62" s="126"/>
+      <c r="H62" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I62" s="48" t="s">
+      <c r="I62" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J62" s="70"/>
-      <c r="K62" s="70"/>
-      <c r="L62" s="70"/>
-      <c r="M62" s="70"/>
-      <c r="N62" s="70"/>
-      <c r="O62" s="108"/>
-      <c r="P62" s="141"/>
-      <c r="Q62" s="44"/>
-      <c r="R62" s="44"/>
-      <c r="S62" s="44"/>
-      <c r="T62" s="44"/>
-      <c r="U62" s="44"/>
-      <c r="V62" s="44"/>
-      <c r="W62" s="44"/>
-      <c r="X62" s="44"/>
-      <c r="Y62" s="44"/>
-      <c r="Z62" s="142"/>
+      <c r="J62" s="128"/>
+      <c r="K62" s="128"/>
+      <c r="L62" s="128"/>
+      <c r="M62" s="128"/>
+      <c r="N62" s="128"/>
+      <c r="O62" s="129"/>
+      <c r="P62" s="149"/>
+      <c r="Q62" s="150"/>
+      <c r="R62" s="150"/>
+      <c r="S62" s="150"/>
+      <c r="T62" s="150"/>
+      <c r="U62" s="150"/>
+      <c r="V62" s="150"/>
+      <c r="W62" s="150"/>
+      <c r="X62" s="150"/>
+      <c r="Y62" s="150"/>
+      <c r="Z62" s="151"/>
     </row>
     <row r="63" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="87" t="s">
+      <c r="A63" s="27" t="s">
         <v>5</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="38" t="s">
+      <c r="C63" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="39"/>
-      <c r="E63" s="88"/>
-      <c r="F63" s="107" t="s">
+      <c r="D63" s="102"/>
+      <c r="E63" s="103"/>
+      <c r="F63" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G63" s="69"/>
-      <c r="H63" s="68" t="s">
+      <c r="G63" s="126"/>
+      <c r="H63" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I63" s="48" t="s">
+      <c r="I63" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J63" s="70"/>
-      <c r="K63" s="70"/>
-      <c r="L63" s="70"/>
-      <c r="M63" s="70"/>
-      <c r="N63" s="70"/>
-      <c r="O63" s="108"/>
-      <c r="P63" s="137" t="s">
+      <c r="J63" s="128"/>
+      <c r="K63" s="128"/>
+      <c r="L63" s="128"/>
+      <c r="M63" s="128"/>
+      <c r="N63" s="128"/>
+      <c r="O63" s="129"/>
+      <c r="P63" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="Q63" s="31"/>
-      <c r="R63" s="31"/>
-      <c r="S63" s="31"/>
-      <c r="T63" s="31"/>
-      <c r="U63" s="31"/>
-      <c r="V63" s="31"/>
-      <c r="W63" s="31"/>
-      <c r="X63" s="31"/>
-      <c r="Y63" s="31"/>
-      <c r="Z63" s="138"/>
+      <c r="Q63" s="120"/>
+      <c r="R63" s="120"/>
+      <c r="S63" s="120"/>
+      <c r="T63" s="120"/>
+      <c r="U63" s="120"/>
+      <c r="V63" s="120"/>
+      <c r="W63" s="120"/>
+      <c r="X63" s="120"/>
+      <c r="Y63" s="120"/>
+      <c r="Z63" s="121"/>
     </row>
     <row r="64" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="87" t="s">
+      <c r="A64" s="27" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C64" s="38" t="s">
+      <c r="C64" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D64" s="39"/>
-      <c r="E64" s="88"/>
-      <c r="F64" s="107" t="s">
+      <c r="D64" s="102"/>
+      <c r="E64" s="103"/>
+      <c r="F64" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G64" s="69"/>
-      <c r="H64" s="68" t="s">
+      <c r="G64" s="126"/>
+      <c r="H64" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I64" s="48" t="s">
+      <c r="I64" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J64" s="70"/>
-      <c r="K64" s="70"/>
-      <c r="L64" s="70"/>
-      <c r="M64" s="70"/>
-      <c r="N64" s="70"/>
-      <c r="O64" s="108"/>
-      <c r="P64" s="143"/>
-      <c r="Q64" s="43"/>
-      <c r="R64" s="43"/>
-      <c r="S64" s="43"/>
-      <c r="T64" s="43"/>
-      <c r="U64" s="43"/>
-      <c r="V64" s="43"/>
-      <c r="W64" s="43"/>
-      <c r="X64" s="43"/>
-      <c r="Y64" s="43"/>
-      <c r="Z64" s="144"/>
+      <c r="J64" s="128"/>
+      <c r="K64" s="128"/>
+      <c r="L64" s="128"/>
+      <c r="M64" s="128"/>
+      <c r="N64" s="128"/>
+      <c r="O64" s="129"/>
+      <c r="P64" s="167"/>
+      <c r="Q64" s="48"/>
+      <c r="R64" s="48"/>
+      <c r="S64" s="48"/>
+      <c r="T64" s="48"/>
+      <c r="U64" s="48"/>
+      <c r="V64" s="48"/>
+      <c r="W64" s="48"/>
+      <c r="X64" s="48"/>
+      <c r="Y64" s="48"/>
+      <c r="Z64" s="168"/>
     </row>
     <row r="65" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="87" t="s">
+      <c r="A65" s="27" t="s">
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="38" t="s">
+      <c r="C65" s="95" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="39"/>
-      <c r="E65" s="88"/>
-      <c r="F65" s="107" t="s">
+      <c r="D65" s="102"/>
+      <c r="E65" s="103"/>
+      <c r="F65" s="125" t="s">
         <v>102</v>
       </c>
-      <c r="G65" s="69"/>
-      <c r="H65" s="68" t="s">
+      <c r="G65" s="126"/>
+      <c r="H65" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I65" s="48" t="s">
+      <c r="I65" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="J65" s="70"/>
-      <c r="K65" s="70"/>
-      <c r="L65" s="70"/>
-      <c r="M65" s="70"/>
-      <c r="N65" s="70"/>
-      <c r="O65" s="108"/>
-      <c r="P65" s="139" t="s">
+      <c r="J65" s="128"/>
+      <c r="K65" s="128"/>
+      <c r="L65" s="128"/>
+      <c r="M65" s="128"/>
+      <c r="N65" s="128"/>
+      <c r="O65" s="129"/>
+      <c r="P65" s="130" t="s">
         <v>82</v>
       </c>
-      <c r="Q65" s="25"/>
-      <c r="R65" s="25"/>
-      <c r="S65" s="25"/>
-      <c r="T65" s="25"/>
-      <c r="U65" s="25"/>
-      <c r="V65" s="25"/>
-      <c r="W65" s="26"/>
-      <c r="X65" s="24" t="s">
+      <c r="Q65" s="131"/>
+      <c r="R65" s="131"/>
+      <c r="S65" s="131"/>
+      <c r="T65" s="131"/>
+      <c r="U65" s="131"/>
+      <c r="V65" s="131"/>
+      <c r="W65" s="152"/>
+      <c r="X65" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="Y65" s="25"/>
-      <c r="Z65" s="140"/>
+      <c r="Y65" s="131"/>
+      <c r="Z65" s="132"/>
     </row>
     <row r="66" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="87" t="s">
+      <c r="A66" s="27" t="s">
         <v>8</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="41" t="s">
+      <c r="C66" s="154" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="42"/>
-      <c r="E66" s="89"/>
-      <c r="F66" s="109" t="s">
+      <c r="D66" s="155"/>
+      <c r="E66" s="156"/>
+      <c r="F66" s="157" t="s">
         <v>102</v>
       </c>
-      <c r="G66" s="110"/>
-      <c r="H66" s="111" t="s">
+      <c r="G66" s="158"/>
+      <c r="H66" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="I66" s="112" t="s">
+      <c r="I66" s="159" t="s">
         <v>108</v>
       </c>
-      <c r="J66" s="113"/>
-      <c r="K66" s="113"/>
-      <c r="L66" s="113"/>
-      <c r="M66" s="113"/>
-      <c r="N66" s="113"/>
-      <c r="O66" s="114"/>
-      <c r="P66" s="145"/>
-      <c r="Q66" s="146"/>
-      <c r="R66" s="146"/>
-      <c r="S66" s="146"/>
-      <c r="T66" s="146"/>
-      <c r="U66" s="146"/>
-      <c r="V66" s="146"/>
-      <c r="W66" s="147"/>
-      <c r="X66" s="148"/>
-      <c r="Y66" s="146"/>
-      <c r="Z66" s="149"/>
+      <c r="J66" s="160"/>
+      <c r="K66" s="160"/>
+      <c r="L66" s="160"/>
+      <c r="M66" s="160"/>
+      <c r="N66" s="160"/>
+      <c r="O66" s="161"/>
+      <c r="P66" s="162"/>
+      <c r="Q66" s="163"/>
+      <c r="R66" s="163"/>
+      <c r="S66" s="163"/>
+      <c r="T66" s="163"/>
+      <c r="U66" s="163"/>
+      <c r="V66" s="163"/>
+      <c r="W66" s="164"/>
+      <c r="X66" s="165"/>
+      <c r="Y66" s="163"/>
+      <c r="Z66" s="166"/>
     </row>
     <row r="67" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="84" t="s">
+      <c r="A67" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="34"/>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="85"/>
-      <c r="F67" s="150">
+      <c r="B67" s="123"/>
+      <c r="C67" s="123"/>
+      <c r="D67" s="123"/>
+      <c r="E67" s="124"/>
+      <c r="F67" s="189">
         <v>0</v>
       </c>
-      <c r="G67" s="115"/>
-      <c r="H67" s="115"/>
-      <c r="I67" s="115"/>
-      <c r="J67" s="115"/>
-      <c r="K67" s="115"/>
-      <c r="L67" s="115"/>
-      <c r="M67" s="115"/>
-      <c r="N67" s="115"/>
-      <c r="O67" s="115"/>
-      <c r="P67" s="115"/>
-      <c r="Q67" s="115"/>
-      <c r="R67" s="115"/>
-      <c r="S67" s="115"/>
-      <c r="T67" s="115"/>
-      <c r="U67" s="115"/>
-      <c r="V67" s="115"/>
-      <c r="W67" s="115"/>
-      <c r="X67" s="115"/>
-      <c r="Y67" s="115"/>
-      <c r="Z67" s="151"/>
+      <c r="G67" s="190"/>
+      <c r="H67" s="190"/>
+      <c r="I67" s="190"/>
+      <c r="J67" s="190"/>
+      <c r="K67" s="190"/>
+      <c r="L67" s="190"/>
+      <c r="M67" s="190"/>
+      <c r="N67" s="190"/>
+      <c r="O67" s="190"/>
+      <c r="P67" s="190"/>
+      <c r="Q67" s="190"/>
+      <c r="R67" s="190"/>
+      <c r="S67" s="190"/>
+      <c r="T67" s="190"/>
+      <c r="U67" s="190"/>
+      <c r="V67" s="190"/>
+      <c r="W67" s="190"/>
+      <c r="X67" s="190"/>
+      <c r="Y67" s="190"/>
+      <c r="Z67" s="191"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="90" t="s">
+      <c r="A68" s="183" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="91"/>
-      <c r="F68" s="99" t="s">
+      <c r="B68" s="184"/>
+      <c r="C68" s="184"/>
+      <c r="D68" s="184"/>
+      <c r="E68" s="185"/>
+      <c r="F68" s="137" t="s">
         <v>74</v>
       </c>
-      <c r="G68" s="117"/>
-      <c r="H68" s="126" t="s">
+      <c r="G68" s="192"/>
+      <c r="H68" s="197" t="s">
         <v>84</v>
       </c>
-      <c r="I68" s="116"/>
-      <c r="J68" s="116"/>
-      <c r="K68" s="116"/>
-      <c r="L68" s="116"/>
-      <c r="M68" s="116"/>
-      <c r="N68" s="116"/>
-      <c r="O68" s="127"/>
-      <c r="P68" s="117" t="s">
+      <c r="I68" s="198"/>
+      <c r="J68" s="198"/>
+      <c r="K68" s="198"/>
+      <c r="L68" s="198"/>
+      <c r="M68" s="198"/>
+      <c r="N68" s="198"/>
+      <c r="O68" s="199"/>
+      <c r="P68" s="192" t="s">
         <v>85</v>
       </c>
-      <c r="Q68" s="117"/>
-      <c r="R68" s="117"/>
-      <c r="S68" s="117"/>
-      <c r="T68" s="117"/>
-      <c r="U68" s="117"/>
-      <c r="V68" s="117"/>
-      <c r="W68" s="117"/>
-      <c r="X68" s="117"/>
-      <c r="Y68" s="117"/>
-      <c r="Z68" s="118"/>
+      <c r="Q68" s="192"/>
+      <c r="R68" s="192"/>
+      <c r="S68" s="192"/>
+      <c r="T68" s="192"/>
+      <c r="U68" s="192"/>
+      <c r="V68" s="192"/>
+      <c r="W68" s="192"/>
+      <c r="X68" s="192"/>
+      <c r="Y68" s="192"/>
+      <c r="Z68" s="200"/>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A69" s="90" t="s">
+      <c r="A69" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="35"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="91"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="71"/>
-      <c r="H69" s="84" t="s">
+      <c r="B69" s="184"/>
+      <c r="C69" s="184"/>
+      <c r="D69" s="184"/>
+      <c r="E69" s="185"/>
+      <c r="F69" s="193"/>
+      <c r="G69" s="194"/>
+      <c r="H69" s="136" t="s">
         <v>71</v>
       </c>
-      <c r="I69" s="34"/>
-      <c r="J69" s="34"/>
-      <c r="K69" s="34"/>
-      <c r="L69" s="34"/>
-      <c r="M69" s="34"/>
-      <c r="N69" s="34"/>
-      <c r="O69" s="85"/>
-      <c r="P69" s="71"/>
-      <c r="Q69" s="71"/>
-      <c r="R69" s="71"/>
-      <c r="S69" s="71"/>
-      <c r="T69" s="71"/>
-      <c r="U69" s="71"/>
-      <c r="V69" s="71"/>
-      <c r="W69" s="71"/>
-      <c r="X69" s="71"/>
-      <c r="Y69" s="71"/>
-      <c r="Z69" s="120"/>
+      <c r="I69" s="123"/>
+      <c r="J69" s="123"/>
+      <c r="K69" s="123"/>
+      <c r="L69" s="123"/>
+      <c r="M69" s="123"/>
+      <c r="N69" s="123"/>
+      <c r="O69" s="124"/>
+      <c r="P69" s="194"/>
+      <c r="Q69" s="194"/>
+      <c r="R69" s="194"/>
+      <c r="S69" s="194"/>
+      <c r="T69" s="194"/>
+      <c r="U69" s="194"/>
+      <c r="V69" s="194"/>
+      <c r="W69" s="194"/>
+      <c r="X69" s="194"/>
+      <c r="Y69" s="194"/>
+      <c r="Z69" s="201"/>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A70" s="90" t="s">
+      <c r="A70" s="183" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="35"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="91"/>
-      <c r="F70" s="119"/>
-      <c r="G70" s="71"/>
-      <c r="H70" s="84"/>
-      <c r="I70" s="34"/>
-      <c r="J70" s="34"/>
-      <c r="K70" s="34"/>
-      <c r="L70" s="34"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="34"/>
-      <c r="O70" s="85"/>
-      <c r="P70" s="71"/>
-      <c r="Q70" s="71"/>
-      <c r="R70" s="71"/>
-      <c r="S70" s="71"/>
-      <c r="T70" s="71"/>
-      <c r="U70" s="71"/>
-      <c r="V70" s="71"/>
-      <c r="W70" s="71"/>
-      <c r="X70" s="71"/>
-      <c r="Y70" s="71"/>
-      <c r="Z70" s="120"/>
+      <c r="B70" s="184"/>
+      <c r="C70" s="184"/>
+      <c r="D70" s="184"/>
+      <c r="E70" s="185"/>
+      <c r="F70" s="193"/>
+      <c r="G70" s="194"/>
+      <c r="H70" s="136"/>
+      <c r="I70" s="123"/>
+      <c r="J70" s="123"/>
+      <c r="K70" s="123"/>
+      <c r="L70" s="123"/>
+      <c r="M70" s="123"/>
+      <c r="N70" s="123"/>
+      <c r="O70" s="124"/>
+      <c r="P70" s="194"/>
+      <c r="Q70" s="194"/>
+      <c r="R70" s="194"/>
+      <c r="S70" s="194"/>
+      <c r="T70" s="194"/>
+      <c r="U70" s="194"/>
+      <c r="V70" s="194"/>
+      <c r="W70" s="194"/>
+      <c r="X70" s="194"/>
+      <c r="Y70" s="194"/>
+      <c r="Z70" s="201"/>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A71" s="92"/>
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="93"/>
-      <c r="F71" s="119"/>
-      <c r="G71" s="71"/>
-      <c r="H71" s="84" t="s">
+      <c r="A71" s="125"/>
+      <c r="B71" s="227"/>
+      <c r="C71" s="227"/>
+      <c r="D71" s="227"/>
+      <c r="E71" s="228"/>
+      <c r="F71" s="193"/>
+      <c r="G71" s="194"/>
+      <c r="H71" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="I71" s="34"/>
-      <c r="J71" s="34"/>
-      <c r="K71" s="34"/>
-      <c r="L71" s="34"/>
-      <c r="M71" s="34"/>
-      <c r="N71" s="34"/>
-      <c r="O71" s="85"/>
-      <c r="P71" s="71"/>
-      <c r="Q71" s="71"/>
-      <c r="R71" s="71"/>
-      <c r="S71" s="71"/>
-      <c r="T71" s="71"/>
-      <c r="U71" s="71"/>
-      <c r="V71" s="71"/>
-      <c r="W71" s="71"/>
-      <c r="X71" s="71"/>
-      <c r="Y71" s="71"/>
-      <c r="Z71" s="120"/>
+      <c r="I71" s="123"/>
+      <c r="J71" s="123"/>
+      <c r="K71" s="123"/>
+      <c r="L71" s="123"/>
+      <c r="M71" s="123"/>
+      <c r="N71" s="123"/>
+      <c r="O71" s="124"/>
+      <c r="P71" s="194"/>
+      <c r="Q71" s="194"/>
+      <c r="R71" s="194"/>
+      <c r="S71" s="194"/>
+      <c r="T71" s="194"/>
+      <c r="U71" s="194"/>
+      <c r="V71" s="194"/>
+      <c r="W71" s="194"/>
+      <c r="X71" s="194"/>
+      <c r="Y71" s="194"/>
+      <c r="Z71" s="201"/>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A72" s="90" t="s">
+      <c r="A72" s="183" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="91"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="71"/>
-      <c r="H72" s="84"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="34"/>
-      <c r="K72" s="34"/>
-      <c r="L72" s="34"/>
-      <c r="M72" s="34"/>
-      <c r="N72" s="34"/>
-      <c r="O72" s="85"/>
-      <c r="P72" s="71"/>
-      <c r="Q72" s="71"/>
-      <c r="R72" s="71"/>
-      <c r="S72" s="71"/>
-      <c r="T72" s="71"/>
-      <c r="U72" s="71"/>
-      <c r="V72" s="71"/>
-      <c r="W72" s="71"/>
-      <c r="X72" s="71"/>
-      <c r="Y72" s="71"/>
-      <c r="Z72" s="120"/>
+      <c r="B72" s="184"/>
+      <c r="C72" s="184"/>
+      <c r="D72" s="184"/>
+      <c r="E72" s="185"/>
+      <c r="F72" s="193"/>
+      <c r="G72" s="194"/>
+      <c r="H72" s="136"/>
+      <c r="I72" s="123"/>
+      <c r="J72" s="123"/>
+      <c r="K72" s="123"/>
+      <c r="L72" s="123"/>
+      <c r="M72" s="123"/>
+      <c r="N72" s="123"/>
+      <c r="O72" s="124"/>
+      <c r="P72" s="194"/>
+      <c r="Q72" s="194"/>
+      <c r="R72" s="194"/>
+      <c r="S72" s="194"/>
+      <c r="T72" s="194"/>
+      <c r="U72" s="194"/>
+      <c r="V72" s="194"/>
+      <c r="W72" s="194"/>
+      <c r="X72" s="194"/>
+      <c r="Y72" s="194"/>
+      <c r="Z72" s="201"/>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A73" s="92"/>
-      <c r="B73" s="32"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="93"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="71"/>
-      <c r="H73" s="128" t="s">
+      <c r="A73" s="181"/>
+      <c r="B73" s="61"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="61"/>
+      <c r="E73" s="182"/>
+      <c r="F73" s="193"/>
+      <c r="G73" s="194"/>
+      <c r="H73" s="186" t="s">
         <v>73</v>
       </c>
-      <c r="I73" s="36"/>
-      <c r="J73" s="36"/>
-      <c r="K73" s="36"/>
-      <c r="L73" s="36"/>
-      <c r="M73" s="36"/>
-      <c r="N73" s="36"/>
-      <c r="O73" s="129"/>
-      <c r="P73" s="71"/>
-      <c r="Q73" s="71"/>
-      <c r="R73" s="71"/>
-      <c r="S73" s="71"/>
-      <c r="T73" s="71"/>
-      <c r="U73" s="71"/>
-      <c r="V73" s="71"/>
-      <c r="W73" s="71"/>
-      <c r="X73" s="71"/>
-      <c r="Y73" s="71"/>
-      <c r="Z73" s="120"/>
+      <c r="I73" s="187"/>
+      <c r="J73" s="187"/>
+      <c r="K73" s="187"/>
+      <c r="L73" s="187"/>
+      <c r="M73" s="187"/>
+      <c r="N73" s="187"/>
+      <c r="O73" s="188"/>
+      <c r="P73" s="194"/>
+      <c r="Q73" s="194"/>
+      <c r="R73" s="194"/>
+      <c r="S73" s="194"/>
+      <c r="T73" s="194"/>
+      <c r="U73" s="194"/>
+      <c r="V73" s="194"/>
+      <c r="W73" s="194"/>
+      <c r="X73" s="194"/>
+      <c r="Y73" s="194"/>
+      <c r="Z73" s="201"/>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A74" s="94" t="s">
+      <c r="A74" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="95"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="71"/>
-      <c r="H74" s="130"/>
-      <c r="I74" s="121"/>
-      <c r="J74" s="121"/>
-      <c r="K74" s="121"/>
-      <c r="L74" s="121"/>
-      <c r="M74" s="121"/>
-      <c r="N74" s="121"/>
-      <c r="O74" s="131"/>
-      <c r="P74" s="71"/>
-      <c r="Q74" s="71"/>
-      <c r="R74" s="71"/>
-      <c r="S74" s="71"/>
-      <c r="T74" s="71"/>
-      <c r="U74" s="71"/>
-      <c r="V74" s="71"/>
-      <c r="W74" s="71"/>
-      <c r="X74" s="71"/>
-      <c r="Y74" s="71"/>
-      <c r="Z74" s="120"/>
+      <c r="B74" s="170"/>
+      <c r="C74" s="170"/>
+      <c r="D74" s="170"/>
+      <c r="E74" s="171"/>
+      <c r="F74" s="193"/>
+      <c r="G74" s="194"/>
+      <c r="H74" s="172"/>
+      <c r="I74" s="173"/>
+      <c r="J74" s="173"/>
+      <c r="K74" s="173"/>
+      <c r="L74" s="173"/>
+      <c r="M74" s="173"/>
+      <c r="N74" s="173"/>
+      <c r="O74" s="174"/>
+      <c r="P74" s="194"/>
+      <c r="Q74" s="194"/>
+      <c r="R74" s="194"/>
+      <c r="S74" s="194"/>
+      <c r="T74" s="194"/>
+      <c r="U74" s="194"/>
+      <c r="V74" s="194"/>
+      <c r="W74" s="194"/>
+      <c r="X74" s="194"/>
+      <c r="Y74" s="194"/>
+      <c r="Z74" s="201"/>
     </row>
     <row r="75" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="96"/>
-      <c r="B75" s="97"/>
-      <c r="C75" s="97"/>
-      <c r="D75" s="97"/>
-      <c r="E75" s="98"/>
-      <c r="F75" s="122"/>
-      <c r="G75" s="124"/>
-      <c r="H75" s="132"/>
-      <c r="I75" s="123"/>
-      <c r="J75" s="123"/>
-      <c r="K75" s="123"/>
-      <c r="L75" s="123"/>
-      <c r="M75" s="123"/>
-      <c r="N75" s="123"/>
-      <c r="O75" s="133"/>
-      <c r="P75" s="124"/>
-      <c r="Q75" s="124"/>
-      <c r="R75" s="124"/>
-      <c r="S75" s="124"/>
-      <c r="T75" s="124"/>
-      <c r="U75" s="124"/>
-      <c r="V75" s="124"/>
-      <c r="W75" s="124"/>
-      <c r="X75" s="124"/>
-      <c r="Y75" s="124"/>
-      <c r="Z75" s="125"/>
+      <c r="A75" s="175"/>
+      <c r="B75" s="176"/>
+      <c r="C75" s="176"/>
+      <c r="D75" s="176"/>
+      <c r="E75" s="177"/>
+      <c r="F75" s="195"/>
+      <c r="G75" s="196"/>
+      <c r="H75" s="178"/>
+      <c r="I75" s="179"/>
+      <c r="J75" s="179"/>
+      <c r="K75" s="179"/>
+      <c r="L75" s="179"/>
+      <c r="M75" s="179"/>
+      <c r="N75" s="179"/>
+      <c r="O75" s="180"/>
+      <c r="P75" s="196"/>
+      <c r="Q75" s="196"/>
+      <c r="R75" s="196"/>
+      <c r="S75" s="196"/>
+      <c r="T75" s="196"/>
+      <c r="U75" s="196"/>
+      <c r="V75" s="196"/>
+      <c r="W75" s="196"/>
+      <c r="X75" s="196"/>
+      <c r="Y75" s="196"/>
+      <c r="Z75" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="259">
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:H5"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:Z3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:X7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:Z8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="N10:Z10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="N11:Z11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:M9"/>
-    <mergeCell ref="N9:U9"/>
-    <mergeCell ref="V9:Z9"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="K12:M13"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:C15"/>
-    <mergeCell ref="D12:E15"/>
-    <mergeCell ref="F12:G15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="W21:Z21"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="W26:Z26"/>
-    <mergeCell ref="W27:Z27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="W25:Z25"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="W30:Z30"/>
-    <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="W28:Z28"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="W34:Z34"/>
-    <mergeCell ref="W35:Z35"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="W32:Z32"/>
-    <mergeCell ref="W33:Z33"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="W38:Z38"/>
-    <mergeCell ref="W39:Z39"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="W36:Z36"/>
-    <mergeCell ref="W37:Z37"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="W42:Z42"/>
-    <mergeCell ref="W43:Z43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="W40:Z40"/>
-    <mergeCell ref="W41:Z41"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="W46:Z46"/>
-    <mergeCell ref="W47:Z47"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="W44:Z44"/>
-    <mergeCell ref="W45:Z45"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="A51:E55"/>
-    <mergeCell ref="F51:M51"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="P57:Z57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:O58"/>
-    <mergeCell ref="P58:Z58"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="F56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I56:O57"/>
-    <mergeCell ref="P56:Z56"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="I61:O61"/>
-    <mergeCell ref="P61:Z61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="I62:O62"/>
-    <mergeCell ref="P62:Z62"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="I59:O59"/>
-    <mergeCell ref="P59:Z59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="I60:O60"/>
-    <mergeCell ref="P60:Z60"/>
-    <mergeCell ref="I65:O65"/>
-    <mergeCell ref="P65:W65"/>
-    <mergeCell ref="X65:Z65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="I66:O66"/>
-    <mergeCell ref="P66:W66"/>
-    <mergeCell ref="X66:Z66"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="I63:O63"/>
-    <mergeCell ref="P63:Z63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="I64:O64"/>
-    <mergeCell ref="P64:Z64"/>
+    <mergeCell ref="W50:Z50"/>
+    <mergeCell ref="W51:Z51"/>
+    <mergeCell ref="W52:Z52"/>
+    <mergeCell ref="W53:Z53"/>
+    <mergeCell ref="W54:Z54"/>
+    <mergeCell ref="W55:Z55"/>
+    <mergeCell ref="W12:Z15"/>
+    <mergeCell ref="W16:Z16"/>
+    <mergeCell ref="W17:Z17"/>
+    <mergeCell ref="W18:Z18"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="W20:Z20"/>
+    <mergeCell ref="W48:Z48"/>
+    <mergeCell ref="W49:Z49"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="H74:O74"/>
     <mergeCell ref="A75:E75"/>
@@ -7230,20 +7023,227 @@
     <mergeCell ref="H70:O70"/>
     <mergeCell ref="C65:E65"/>
     <mergeCell ref="F65:G65"/>
-    <mergeCell ref="W50:Z50"/>
-    <mergeCell ref="W51:Z51"/>
-    <mergeCell ref="W52:Z52"/>
-    <mergeCell ref="W53:Z53"/>
-    <mergeCell ref="W54:Z54"/>
-    <mergeCell ref="W55:Z55"/>
-    <mergeCell ref="W12:Z15"/>
-    <mergeCell ref="W16:Z16"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="W18:Z18"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="W20:Z20"/>
-    <mergeCell ref="W48:Z48"/>
-    <mergeCell ref="W49:Z49"/>
+    <mergeCell ref="I65:O65"/>
+    <mergeCell ref="P65:W65"/>
+    <mergeCell ref="X65:Z65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="P66:W66"/>
+    <mergeCell ref="X66:Z66"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="I63:O63"/>
+    <mergeCell ref="P63:Z63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="I64:O64"/>
+    <mergeCell ref="P64:Z64"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="I61:O61"/>
+    <mergeCell ref="P61:Z61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="I62:O62"/>
+    <mergeCell ref="P62:Z62"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="I59:O59"/>
+    <mergeCell ref="P59:Z59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="I60:O60"/>
+    <mergeCell ref="P60:Z60"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="P57:Z57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:O58"/>
+    <mergeCell ref="P58:Z58"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="F56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:O57"/>
+    <mergeCell ref="P56:Z56"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="A51:E55"/>
+    <mergeCell ref="F51:M51"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="W46:Z46"/>
+    <mergeCell ref="W47:Z47"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="W44:Z44"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="W42:Z42"/>
+    <mergeCell ref="W43:Z43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="W40:Z40"/>
+    <mergeCell ref="W41:Z41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="W38:Z38"/>
+    <mergeCell ref="W39:Z39"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="W36:Z36"/>
+    <mergeCell ref="W37:Z37"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="W34:Z34"/>
+    <mergeCell ref="W35:Z35"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="W32:Z32"/>
+    <mergeCell ref="W33:Z33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="W30:Z30"/>
+    <mergeCell ref="W31:Z31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="W28:Z28"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="W26:Z26"/>
+    <mergeCell ref="W27:Z27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="W25:Z25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="W21:Z21"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="N11:Z11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:M9"/>
+    <mergeCell ref="N9:U9"/>
+    <mergeCell ref="V9:Z9"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="K12:M13"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:C15"/>
+    <mergeCell ref="D12:E15"/>
+    <mergeCell ref="F12:G15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:X7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:Z8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="N10:Z10"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:H5"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:Z3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.1" right="0" top="0.1" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="14" scale="74" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/Resumen_1ro_2do.xlsx
+++ b/backend/templates/Resumen_1ro_2do.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JavierWorkSpace\BatallaProject\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6445754-FCC8-461B-97D0-ED95D0BCB9DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12EB1E3-3118-450D-B474-2002884A828F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21555" yWindow="1080" windowWidth="20070" windowHeight="17205" xr2:uid="{299BAFB4-AE58-4015-B36E-D7CD92F1B4DD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{299BAFB4-AE58-4015-B36E-D7CD92F1B4DD}"/>
   </bookViews>
   <sheets>
     <sheet name="1er Año" sheetId="5" r:id="rId1"/>
@@ -2112,7 +2112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2173,9 +2173,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2184,9 +2181,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2233,6 +2227,9 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2470,20 +2467,14 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2567,19 +2558,19 @@
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
+      <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2627,20 +2618,29 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2691,9 +2691,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -2745,12 +2742,6 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3142,116 +3133,116 @@
   <sheetData>
     <row r="1" spans="1:28" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H1" s="9"/>
-      <c r="N1" s="46" t="s">
+      <c r="N1" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="46"/>
-      <c r="P1" s="46"/>
-      <c r="Q1" s="46"/>
-      <c r="R1" s="46"/>
-      <c r="S1" s="46"/>
-      <c r="T1" s="46"/>
-      <c r="U1" s="46"/>
-      <c r="V1" s="46"/>
-      <c r="W1" s="46"/>
-      <c r="X1" s="46"/>
-      <c r="Y1" s="46"/>
+      <c r="O1" s="45"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="45"/>
+      <c r="U1" s="45"/>
+      <c r="V1" s="45"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
     </row>
     <row r="2" spans="1:28" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="N2" s="48" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="N2" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="48"/>
-      <c r="S2" s="48"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="48"/>
-      <c r="Y2" s="48"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
     </row>
     <row r="3" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="49" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="50"/>
-      <c r="Q3" s="50"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="50"/>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
-      <c r="V3" s="50"/>
-      <c r="W3" s="50"/>
-      <c r="X3" s="50"/>
-      <c r="Y3" s="50"/>
-      <c r="Z3" s="50"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
     </row>
     <row r="4" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="49" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="49"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="51" t="s">
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
       <c r="Z4" s="10"/>
     </row>
     <row r="5" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -3272,12 +3263,12 @@
       <c r="Z5" s="5"/>
     </row>
     <row r="6" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="52" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -3302,263 +3293,263 @@
       <c r="Z6" s="5"/>
     </row>
     <row r="7" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="54"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="55" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="54" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="55"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-      <c r="W7" s="56"/>
-      <c r="X7" s="56"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="55"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="55"/>
+      <c r="T7" s="55"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="55"/>
+      <c r="W7" s="55"/>
+      <c r="X7" s="55"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
     <row r="8" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="57" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="S8" s="57"/>
-      <c r="T8" s="57"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
+      <c r="Z8" s="49"/>
     </row>
     <row r="9" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="61"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="60"/>
       <c r="F9" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="57" t="s">
+      <c r="G9" s="60"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
-      <c r="M9" s="57"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="57"/>
-      <c r="W9" s="57"/>
-      <c r="X9" s="57"/>
-      <c r="Y9" s="57"/>
-      <c r="Z9" s="57"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
     </row>
     <row r="10" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="55" t="s">
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="54"/>
-      <c r="O10" s="54"/>
-      <c r="P10" s="54"/>
-      <c r="Q10" s="54"/>
-      <c r="R10" s="54"/>
-      <c r="S10" s="54"/>
-      <c r="T10" s="54"/>
-      <c r="U10" s="54"/>
-      <c r="V10" s="54"/>
-      <c r="W10" s="54"/>
-      <c r="X10" s="54"/>
-      <c r="Y10" s="54"/>
-      <c r="Z10" s="54"/>
+      <c r="J10" s="54"/>
+      <c r="K10" s="54"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="53"/>
+      <c r="T10" s="53"/>
+      <c r="U10" s="53"/>
+      <c r="V10" s="53"/>
+      <c r="W10" s="53"/>
+      <c r="X10" s="53"/>
+      <c r="Y10" s="53"/>
+      <c r="Z10" s="53"/>
     </row>
     <row r="11" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="60"/>
-      <c r="N11" s="59" t="s">
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
-      <c r="S11" s="59"/>
-      <c r="T11" s="59"/>
-      <c r="U11" s="59"/>
-      <c r="V11" s="59"/>
-      <c r="W11" s="59"/>
-      <c r="X11" s="59"/>
-      <c r="Y11" s="59"/>
-      <c r="Z11" s="60"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="58"/>
+      <c r="Q11" s="58"/>
+      <c r="R11" s="58"/>
+      <c r="S11" s="58"/>
+      <c r="T11" s="58"/>
+      <c r="U11" s="58"/>
+      <c r="V11" s="58"/>
+      <c r="W11" s="58"/>
+      <c r="X11" s="58"/>
+      <c r="Y11" s="58"/>
+      <c r="Z11" s="59"/>
     </row>
     <row r="12" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="84" t="s">
+      <c r="C12" s="78"/>
+      <c r="D12" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="85"/>
-      <c r="F12" s="84" t="s">
+      <c r="E12" s="84"/>
+      <c r="F12" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="85"/>
-      <c r="H12" s="90" t="s">
+      <c r="G12" s="84"/>
+      <c r="H12" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="75" t="s">
+      <c r="I12" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="62" t="s">
+      <c r="J12" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="65" t="s">
+      <c r="K12" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="66"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="117" t="s">
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="116" t="s">
         <v>49</v>
       </c>
-      <c r="O12" s="117"/>
-      <c r="P12" s="117"/>
-      <c r="Q12" s="117"/>
-      <c r="R12" s="117"/>
-      <c r="S12" s="117"/>
-      <c r="T12" s="117"/>
-      <c r="U12" s="117"/>
-      <c r="V12" s="117"/>
-      <c r="W12" s="215" t="s">
+      <c r="O12" s="116"/>
+      <c r="P12" s="116"/>
+      <c r="Q12" s="116"/>
+      <c r="R12" s="116"/>
+      <c r="S12" s="116"/>
+      <c r="T12" s="116"/>
+      <c r="U12" s="116"/>
+      <c r="V12" s="116"/>
+      <c r="W12" s="214" t="s">
         <v>50</v>
       </c>
-      <c r="X12" s="216"/>
-      <c r="Y12" s="216"/>
-      <c r="Z12" s="217"/>
+      <c r="X12" s="215"/>
+      <c r="Y12" s="215"/>
+      <c r="Z12" s="216"/>
     </row>
     <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="76"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
-      <c r="D13" s="86"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="76"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="69"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="120" t="s">
+      <c r="A13" s="75"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="68"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="119" t="s">
         <v>48</v>
       </c>
-      <c r="O13" s="120"/>
-      <c r="P13" s="120"/>
-      <c r="Q13" s="120"/>
-      <c r="R13" s="120"/>
-      <c r="S13" s="120"/>
-      <c r="T13" s="120"/>
-      <c r="U13" s="120"/>
-      <c r="V13" s="120"/>
-      <c r="W13" s="218"/>
-      <c r="X13" s="219"/>
-      <c r="Y13" s="219"/>
-      <c r="Z13" s="220"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="119"/>
+      <c r="R13" s="119"/>
+      <c r="S13" s="119"/>
+      <c r="T13" s="119"/>
+      <c r="U13" s="119"/>
+      <c r="V13" s="119"/>
+      <c r="W13" s="217"/>
+      <c r="X13" s="218"/>
+      <c r="Y13" s="218"/>
+      <c r="Z13" s="219"/>
     </row>
     <row r="14" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="76"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="81"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="86"/>
-      <c r="G14" s="87"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="71" t="s">
+      <c r="A14" s="75"/>
+      <c r="B14" s="79"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="86"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="75"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="L14" s="71" t="s">
+      <c r="L14" s="70" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="73" t="s">
+      <c r="M14" s="72" t="s">
         <v>44</v>
       </c>
       <c r="N14" s="16" t="s">
@@ -3588,77 +3579,77 @@
       <c r="V14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="W14" s="218"/>
-      <c r="X14" s="219"/>
-      <c r="Y14" s="219"/>
-      <c r="Z14" s="220"/>
+      <c r="W14" s="217"/>
+      <c r="X14" s="218"/>
+      <c r="Y14" s="218"/>
+      <c r="Z14" s="219"/>
     </row>
     <row r="15" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="77"/>
-      <c r="B15" s="82"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="89"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="72"/>
-      <c r="L15" s="72"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="43" t="s">
-        <v>104</v>
-      </c>
-      <c r="O15" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="P15" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q15" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="R15" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="S15" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="T15" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="U15" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="V15" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="W15" s="221"/>
-      <c r="X15" s="222"/>
-      <c r="Y15" s="222"/>
-      <c r="Z15" s="223"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="O15" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q15" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="S15" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="T15" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="U15" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="V15" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="W15" s="220"/>
+      <c r="X15" s="221"/>
+      <c r="Y15" s="221"/>
+      <c r="Z15" s="222"/>
     </row>
     <row r="16" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="97" t="s">
+      <c r="B16" s="96" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="98"/>
-      <c r="D16" s="99" t="s">
+      <c r="C16" s="97"/>
+      <c r="D16" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="100"/>
-      <c r="F16" s="99" t="s">
+      <c r="E16" s="99"/>
+      <c r="F16" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="100"/>
-      <c r="H16" s="36" t="s">
+      <c r="G16" s="99"/>
+      <c r="H16" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="I16" s="44" t="s">
+      <c r="I16" s="42" t="s">
         <v>104</v>
       </c>
       <c r="J16" s="19" t="s">
@@ -3670,7 +3661,7 @@
       <c r="L16" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="45" t="s">
+      <c r="M16" s="43" t="s">
         <v>104</v>
       </c>
       <c r="N16" s="23" t="s">
@@ -3700,34 +3691,34 @@
       <c r="V16" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="W16" s="224" t="s">
+      <c r="W16" s="223" t="s">
         <v>105</v>
       </c>
-      <c r="X16" s="225"/>
-      <c r="Y16" s="225"/>
-      <c r="Z16" s="226"/>
+      <c r="X16" s="224"/>
+      <c r="Y16" s="224"/>
+      <c r="Z16" s="225"/>
       <c r="AB16" s="6"/>
     </row>
     <row r="17" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="94"/>
-      <c r="D17" s="95" t="s">
+      <c r="C17" s="93"/>
+      <c r="D17" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="96"/>
-      <c r="F17" s="95" t="s">
+      <c r="E17" s="95"/>
+      <c r="F17" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="96"/>
+      <c r="G17" s="95"/>
       <c r="H17" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="I17" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J17" s="4" t="s">
@@ -3739,7 +3730,7 @@
       <c r="L17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M17" s="32" t="s">
+      <c r="M17" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N17" s="14" t="s">
@@ -3769,34 +3760,34 @@
       <c r="V17" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W17" s="101" t="s">
+      <c r="W17" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X17" s="102"/>
-      <c r="Y17" s="102"/>
-      <c r="Z17" s="103"/>
+      <c r="X17" s="101"/>
+      <c r="Y17" s="101"/>
+      <c r="Z17" s="102"/>
       <c r="AC17" s="7"/>
     </row>
     <row r="18" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="41" t="s">
+      <c r="A18" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="93" t="s">
+      <c r="B18" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="94"/>
-      <c r="D18" s="95" t="s">
+      <c r="C18" s="93"/>
+      <c r="D18" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="96"/>
-      <c r="F18" s="95" t="s">
+      <c r="E18" s="95"/>
+      <c r="F18" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="96"/>
+      <c r="G18" s="95"/>
       <c r="H18" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J18" s="4" t="s">
@@ -3808,7 +3799,7 @@
       <c r="L18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M18" s="32" t="s">
+      <c r="M18" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N18" s="14" t="s">
@@ -3838,33 +3829,33 @@
       <c r="V18" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W18" s="101" t="s">
+      <c r="W18" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X18" s="102"/>
-      <c r="Y18" s="102"/>
-      <c r="Z18" s="103"/>
+      <c r="X18" s="101"/>
+      <c r="Y18" s="101"/>
+      <c r="Z18" s="102"/>
     </row>
     <row r="19" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="41" t="s">
+      <c r="A19" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="94"/>
-      <c r="D19" s="95" t="s">
+      <c r="C19" s="93"/>
+      <c r="D19" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="96"/>
-      <c r="F19" s="95" t="s">
+      <c r="E19" s="95"/>
+      <c r="F19" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="96"/>
+      <c r="G19" s="95"/>
       <c r="H19" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="27" t="s">
+      <c r="I19" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J19" s="4" t="s">
@@ -3876,7 +3867,7 @@
       <c r="L19" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="32" t="s">
+      <c r="M19" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N19" s="14" t="s">
@@ -3906,33 +3897,33 @@
       <c r="V19" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W19" s="101" t="s">
+      <c r="W19" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X19" s="102"/>
-      <c r="Y19" s="102"/>
-      <c r="Z19" s="103"/>
+      <c r="X19" s="101"/>
+      <c r="Y19" s="101"/>
+      <c r="Z19" s="102"/>
     </row>
     <row r="20" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="41" t="s">
+      <c r="A20" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="94"/>
-      <c r="D20" s="95" t="s">
+      <c r="C20" s="93"/>
+      <c r="D20" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="96"/>
-      <c r="F20" s="95" t="s">
+      <c r="E20" s="95"/>
+      <c r="F20" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="96"/>
+      <c r="G20" s="95"/>
       <c r="H20" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J20" s="4" t="s">
@@ -3944,7 +3935,7 @@
       <c r="L20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="32" t="s">
+      <c r="M20" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N20" s="14" t="s">
@@ -3974,33 +3965,33 @@
       <c r="V20" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W20" s="101" t="s">
+      <c r="W20" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X20" s="102"/>
-      <c r="Y20" s="102"/>
-      <c r="Z20" s="103"/>
+      <c r="X20" s="101"/>
+      <c r="Y20" s="101"/>
+      <c r="Z20" s="102"/>
     </row>
     <row r="21" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="41" t="s">
+      <c r="A21" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="93" t="s">
+      <c r="B21" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="94"/>
-      <c r="D21" s="95" t="s">
+      <c r="C21" s="93"/>
+      <c r="D21" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="96"/>
-      <c r="F21" s="95" t="s">
+      <c r="E21" s="95"/>
+      <c r="F21" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="96"/>
+      <c r="G21" s="95"/>
       <c r="H21" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I21" s="27" t="s">
+      <c r="I21" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J21" s="4" t="s">
@@ -4012,7 +4003,7 @@
       <c r="L21" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M21" s="32" t="s">
+      <c r="M21" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N21" s="14" t="s">
@@ -4042,33 +4033,33 @@
       <c r="V21" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W21" s="101" t="s">
+      <c r="W21" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X21" s="102"/>
-      <c r="Y21" s="102"/>
-      <c r="Z21" s="103"/>
+      <c r="X21" s="101"/>
+      <c r="Y21" s="101"/>
+      <c r="Z21" s="102"/>
     </row>
     <row r="22" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="94"/>
-      <c r="D22" s="95" t="s">
+      <c r="C22" s="93"/>
+      <c r="D22" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="96"/>
-      <c r="F22" s="95" t="s">
+      <c r="E22" s="95"/>
+      <c r="F22" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="96"/>
+      <c r="G22" s="95"/>
       <c r="H22" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="I22" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J22" s="4" t="s">
@@ -4080,7 +4071,7 @@
       <c r="L22" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M22" s="32" t="s">
+      <c r="M22" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N22" s="14" t="s">
@@ -4110,33 +4101,33 @@
       <c r="V22" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W22" s="101" t="s">
+      <c r="W22" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X22" s="102"/>
-      <c r="Y22" s="102"/>
-      <c r="Z22" s="103"/>
+      <c r="X22" s="101"/>
+      <c r="Y22" s="101"/>
+      <c r="Z22" s="102"/>
     </row>
     <row r="23" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="41" t="s">
+      <c r="A23" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="93" t="s">
+      <c r="B23" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="94"/>
-      <c r="D23" s="95" t="s">
+      <c r="C23" s="93"/>
+      <c r="D23" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="96"/>
-      <c r="F23" s="95" t="s">
+      <c r="E23" s="95"/>
+      <c r="F23" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="96"/>
+      <c r="G23" s="95"/>
       <c r="H23" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="I23" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J23" s="4" t="s">
@@ -4148,7 +4139,7 @@
       <c r="L23" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="32" t="s">
+      <c r="M23" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N23" s="14" t="s">
@@ -4178,33 +4169,33 @@
       <c r="V23" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W23" s="101" t="s">
+      <c r="W23" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X23" s="102"/>
-      <c r="Y23" s="102"/>
-      <c r="Z23" s="103"/>
+      <c r="X23" s="101"/>
+      <c r="Y23" s="101"/>
+      <c r="Z23" s="102"/>
     </row>
     <row r="24" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="94"/>
-      <c r="D24" s="95" t="s">
+      <c r="C24" s="93"/>
+      <c r="D24" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="96"/>
-      <c r="F24" s="95" t="s">
+      <c r="E24" s="95"/>
+      <c r="F24" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="96"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J24" s="4" t="s">
@@ -4216,7 +4207,7 @@
       <c r="L24" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="M24" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N24" s="14" t="s">
@@ -4246,33 +4237,33 @@
       <c r="V24" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W24" s="101" t="s">
+      <c r="W24" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X24" s="102"/>
-      <c r="Y24" s="102"/>
-      <c r="Z24" s="103"/>
+      <c r="X24" s="101"/>
+      <c r="Y24" s="101"/>
+      <c r="Z24" s="102"/>
     </row>
     <row r="25" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="93" t="s">
+      <c r="B25" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="94"/>
-      <c r="D25" s="95" t="s">
+      <c r="C25" s="93"/>
+      <c r="D25" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="96"/>
-      <c r="F25" s="95" t="s">
+      <c r="E25" s="95"/>
+      <c r="F25" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="96"/>
+      <c r="G25" s="95"/>
       <c r="H25" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I25" s="27" t="s">
+      <c r="I25" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J25" s="4" t="s">
@@ -4284,7 +4275,7 @@
       <c r="L25" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M25" s="32" t="s">
+      <c r="M25" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N25" s="14" t="s">
@@ -4314,33 +4305,33 @@
       <c r="V25" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W25" s="101" t="s">
+      <c r="W25" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X25" s="102"/>
-      <c r="Y25" s="102"/>
-      <c r="Z25" s="103"/>
+      <c r="X25" s="101"/>
+      <c r="Y25" s="101"/>
+      <c r="Z25" s="102"/>
     </row>
     <row r="26" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="93" t="s">
+      <c r="B26" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="94"/>
-      <c r="D26" s="95" t="s">
+      <c r="C26" s="93"/>
+      <c r="D26" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="96"/>
-      <c r="F26" s="95" t="s">
+      <c r="E26" s="95"/>
+      <c r="F26" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="96"/>
+      <c r="G26" s="95"/>
       <c r="H26" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I26" s="27" t="s">
+      <c r="I26" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J26" s="4" t="s">
@@ -4352,7 +4343,7 @@
       <c r="L26" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M26" s="32" t="s">
+      <c r="M26" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N26" s="14" t="s">
@@ -4382,33 +4373,33 @@
       <c r="V26" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W26" s="101" t="s">
+      <c r="W26" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X26" s="102"/>
-      <c r="Y26" s="102"/>
-      <c r="Z26" s="103"/>
+      <c r="X26" s="101"/>
+      <c r="Y26" s="101"/>
+      <c r="Z26" s="102"/>
     </row>
     <row r="27" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="41" t="s">
+      <c r="A27" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="93" t="s">
+      <c r="B27" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="94"/>
-      <c r="D27" s="95" t="s">
+      <c r="C27" s="93"/>
+      <c r="D27" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="96"/>
-      <c r="F27" s="95" t="s">
+      <c r="E27" s="95"/>
+      <c r="F27" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="96"/>
+      <c r="G27" s="95"/>
       <c r="H27" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I27" s="27" t="s">
+      <c r="I27" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J27" s="4" t="s">
@@ -4420,7 +4411,7 @@
       <c r="L27" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M27" s="32" t="s">
+      <c r="M27" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N27" s="14" t="s">
@@ -4450,33 +4441,33 @@
       <c r="V27" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W27" s="101" t="s">
+      <c r="W27" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X27" s="102"/>
-      <c r="Y27" s="102"/>
-      <c r="Z27" s="103"/>
+      <c r="X27" s="101"/>
+      <c r="Y27" s="101"/>
+      <c r="Z27" s="102"/>
     </row>
     <row r="28" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="41" t="s">
+      <c r="A28" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="94"/>
-      <c r="D28" s="95" t="s">
+      <c r="C28" s="93"/>
+      <c r="D28" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="96"/>
-      <c r="F28" s="95" t="s">
+      <c r="E28" s="95"/>
+      <c r="F28" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="96"/>
+      <c r="G28" s="95"/>
       <c r="H28" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I28" s="27" t="s">
+      <c r="I28" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J28" s="4" t="s">
@@ -4488,7 +4479,7 @@
       <c r="L28" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M28" s="32" t="s">
+      <c r="M28" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N28" s="14" t="s">
@@ -4518,33 +4509,33 @@
       <c r="V28" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W28" s="101" t="s">
+      <c r="W28" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X28" s="102"/>
-      <c r="Y28" s="102"/>
-      <c r="Z28" s="103"/>
+      <c r="X28" s="101"/>
+      <c r="Y28" s="101"/>
+      <c r="Z28" s="102"/>
     </row>
     <row r="29" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="93" t="s">
+      <c r="B29" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="94"/>
-      <c r="D29" s="95" t="s">
+      <c r="C29" s="93"/>
+      <c r="D29" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="96"/>
-      <c r="F29" s="95" t="s">
+      <c r="E29" s="95"/>
+      <c r="F29" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="96"/>
+      <c r="G29" s="95"/>
       <c r="H29" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I29" s="27" t="s">
+      <c r="I29" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J29" s="4" t="s">
@@ -4556,7 +4547,7 @@
       <c r="L29" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M29" s="32" t="s">
+      <c r="M29" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N29" s="14" t="s">
@@ -4586,33 +4577,33 @@
       <c r="V29" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W29" s="101" t="s">
+      <c r="W29" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X29" s="102"/>
-      <c r="Y29" s="102"/>
-      <c r="Z29" s="103"/>
+      <c r="X29" s="101"/>
+      <c r="Y29" s="101"/>
+      <c r="Z29" s="102"/>
     </row>
     <row r="30" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="41" t="s">
+      <c r="A30" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="93" t="s">
+      <c r="B30" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="94"/>
-      <c r="D30" s="95" t="s">
+      <c r="C30" s="93"/>
+      <c r="D30" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="96"/>
-      <c r="F30" s="95" t="s">
+      <c r="E30" s="95"/>
+      <c r="F30" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G30" s="96"/>
+      <c r="G30" s="95"/>
       <c r="H30" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I30" s="27" t="s">
+      <c r="I30" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J30" s="4" t="s">
@@ -4624,7 +4615,7 @@
       <c r="L30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M30" s="32" t="s">
+      <c r="M30" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N30" s="14" t="s">
@@ -4654,33 +4645,33 @@
       <c r="V30" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W30" s="101" t="s">
+      <c r="W30" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X30" s="102"/>
-      <c r="Y30" s="102"/>
-      <c r="Z30" s="103"/>
+      <c r="X30" s="101"/>
+      <c r="Y30" s="101"/>
+      <c r="Z30" s="102"/>
     </row>
     <row r="31" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="94"/>
-      <c r="D31" s="95" t="s">
+      <c r="C31" s="93"/>
+      <c r="D31" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="96"/>
-      <c r="F31" s="95" t="s">
+      <c r="E31" s="95"/>
+      <c r="F31" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="96"/>
+      <c r="G31" s="95"/>
       <c r="H31" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="27" t="s">
+      <c r="I31" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J31" s="4" t="s">
@@ -4692,7 +4683,7 @@
       <c r="L31" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M31" s="32" t="s">
+      <c r="M31" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N31" s="14" t="s">
@@ -4722,33 +4713,33 @@
       <c r="V31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W31" s="101" t="s">
+      <c r="W31" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X31" s="102"/>
-      <c r="Y31" s="102"/>
-      <c r="Z31" s="103"/>
+      <c r="X31" s="101"/>
+      <c r="Y31" s="101"/>
+      <c r="Z31" s="102"/>
     </row>
     <row r="32" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="41" t="s">
+      <c r="A32" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="93" t="s">
+      <c r="B32" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="94"/>
-      <c r="D32" s="95" t="s">
+      <c r="C32" s="93"/>
+      <c r="D32" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="96"/>
-      <c r="F32" s="95" t="s">
+      <c r="E32" s="95"/>
+      <c r="F32" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="96"/>
+      <c r="G32" s="95"/>
       <c r="H32" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="27" t="s">
+      <c r="I32" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J32" s="4" t="s">
@@ -4760,7 +4751,7 @@
       <c r="L32" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M32" s="32" t="s">
+      <c r="M32" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N32" s="14" t="s">
@@ -4790,33 +4781,33 @@
       <c r="V32" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W32" s="101" t="s">
+      <c r="W32" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X32" s="102"/>
-      <c r="Y32" s="102"/>
-      <c r="Z32" s="103"/>
+      <c r="X32" s="101"/>
+      <c r="Y32" s="101"/>
+      <c r="Z32" s="102"/>
     </row>
     <row r="33" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="41" t="s">
+      <c r="A33" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="93" t="s">
+      <c r="B33" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="94"/>
-      <c r="D33" s="95" t="s">
+      <c r="C33" s="93"/>
+      <c r="D33" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="96"/>
-      <c r="F33" s="95" t="s">
+      <c r="E33" s="95"/>
+      <c r="F33" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G33" s="96"/>
+      <c r="G33" s="95"/>
       <c r="H33" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I33" s="27" t="s">
+      <c r="I33" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J33" s="4" t="s">
@@ -4828,7 +4819,7 @@
       <c r="L33" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M33" s="32" t="s">
+      <c r="M33" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N33" s="14" t="s">
@@ -4858,33 +4849,33 @@
       <c r="V33" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W33" s="101" t="s">
+      <c r="W33" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X33" s="102"/>
-      <c r="Y33" s="102"/>
-      <c r="Z33" s="103"/>
+      <c r="X33" s="101"/>
+      <c r="Y33" s="101"/>
+      <c r="Z33" s="102"/>
     </row>
     <row r="34" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="41" t="s">
+      <c r="A34" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="93" t="s">
+      <c r="B34" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="94"/>
-      <c r="D34" s="95" t="s">
+      <c r="C34" s="93"/>
+      <c r="D34" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="96"/>
-      <c r="F34" s="95" t="s">
+      <c r="E34" s="95"/>
+      <c r="F34" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G34" s="96"/>
+      <c r="G34" s="95"/>
       <c r="H34" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I34" s="27" t="s">
+      <c r="I34" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J34" s="4" t="s">
@@ -4896,7 +4887,7 @@
       <c r="L34" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M34" s="32" t="s">
+      <c r="M34" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N34" s="14" t="s">
@@ -4926,33 +4917,33 @@
       <c r="V34" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W34" s="101" t="s">
+      <c r="W34" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X34" s="102"/>
-      <c r="Y34" s="102"/>
-      <c r="Z34" s="103"/>
+      <c r="X34" s="101"/>
+      <c r="Y34" s="101"/>
+      <c r="Z34" s="102"/>
     </row>
     <row r="35" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="41" t="s">
+      <c r="A35" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="93" t="s">
+      <c r="B35" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="94"/>
-      <c r="D35" s="95" t="s">
+      <c r="C35" s="93"/>
+      <c r="D35" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="96"/>
-      <c r="F35" s="95" t="s">
+      <c r="E35" s="95"/>
+      <c r="F35" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="96"/>
+      <c r="G35" s="95"/>
       <c r="H35" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I35" s="27" t="s">
+      <c r="I35" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J35" s="4" t="s">
@@ -4964,7 +4955,7 @@
       <c r="L35" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M35" s="32" t="s">
+      <c r="M35" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N35" s="14" t="s">
@@ -4994,33 +4985,33 @@
       <c r="V35" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W35" s="101" t="s">
+      <c r="W35" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X35" s="102"/>
-      <c r="Y35" s="102"/>
-      <c r="Z35" s="103"/>
+      <c r="X35" s="101"/>
+      <c r="Y35" s="101"/>
+      <c r="Z35" s="102"/>
     </row>
     <row r="36" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="41" t="s">
+      <c r="A36" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="93" t="s">
+      <c r="B36" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="94"/>
-      <c r="D36" s="95" t="s">
+      <c r="C36" s="93"/>
+      <c r="D36" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="96"/>
-      <c r="F36" s="95" t="s">
+      <c r="E36" s="95"/>
+      <c r="F36" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="96"/>
+      <c r="G36" s="95"/>
       <c r="H36" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I36" s="27" t="s">
+      <c r="I36" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J36" s="4" t="s">
@@ -5032,7 +5023,7 @@
       <c r="L36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M36" s="32" t="s">
+      <c r="M36" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N36" s="14" t="s">
@@ -5062,33 +5053,33 @@
       <c r="V36" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W36" s="101" t="s">
+      <c r="W36" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X36" s="102"/>
-      <c r="Y36" s="102"/>
-      <c r="Z36" s="103"/>
+      <c r="X36" s="101"/>
+      <c r="Y36" s="101"/>
+      <c r="Z36" s="102"/>
     </row>
     <row r="37" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="41" t="s">
+      <c r="A37" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="93" t="s">
+      <c r="B37" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="94"/>
-      <c r="D37" s="95" t="s">
+      <c r="C37" s="93"/>
+      <c r="D37" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="96"/>
-      <c r="F37" s="95" t="s">
+      <c r="E37" s="95"/>
+      <c r="F37" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="96"/>
+      <c r="G37" s="95"/>
       <c r="H37" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I37" s="27" t="s">
+      <c r="I37" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J37" s="4" t="s">
@@ -5100,7 +5091,7 @@
       <c r="L37" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M37" s="32" t="s">
+      <c r="M37" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N37" s="14" t="s">
@@ -5130,33 +5121,33 @@
       <c r="V37" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W37" s="101" t="s">
+      <c r="W37" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X37" s="102"/>
-      <c r="Y37" s="102"/>
-      <c r="Z37" s="103"/>
+      <c r="X37" s="101"/>
+      <c r="Y37" s="101"/>
+      <c r="Z37" s="102"/>
     </row>
     <row r="38" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="93" t="s">
+      <c r="B38" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="94"/>
-      <c r="D38" s="95" t="s">
+      <c r="C38" s="93"/>
+      <c r="D38" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="96"/>
-      <c r="F38" s="95" t="s">
+      <c r="E38" s="95"/>
+      <c r="F38" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="96"/>
+      <c r="G38" s="95"/>
       <c r="H38" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I38" s="27" t="s">
+      <c r="I38" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J38" s="4" t="s">
@@ -5168,7 +5159,7 @@
       <c r="L38" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M38" s="32" t="s">
+      <c r="M38" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N38" s="14" t="s">
@@ -5198,33 +5189,33 @@
       <c r="V38" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W38" s="101" t="s">
+      <c r="W38" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X38" s="102"/>
-      <c r="Y38" s="102"/>
-      <c r="Z38" s="103"/>
+      <c r="X38" s="101"/>
+      <c r="Y38" s="101"/>
+      <c r="Z38" s="102"/>
     </row>
     <row r="39" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="41" t="s">
+      <c r="A39" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="93" t="s">
+      <c r="B39" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="95" t="s">
+      <c r="C39" s="93"/>
+      <c r="D39" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="96"/>
-      <c r="F39" s="95" t="s">
+      <c r="E39" s="95"/>
+      <c r="F39" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="96"/>
+      <c r="G39" s="95"/>
       <c r="H39" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I39" s="27" t="s">
+      <c r="I39" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J39" s="4" t="s">
@@ -5236,7 +5227,7 @@
       <c r="L39" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M39" s="32" t="s">
+      <c r="M39" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N39" s="14" t="s">
@@ -5266,33 +5257,33 @@
       <c r="V39" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W39" s="101" t="s">
+      <c r="W39" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X39" s="102"/>
-      <c r="Y39" s="102"/>
-      <c r="Z39" s="103"/>
+      <c r="X39" s="101"/>
+      <c r="Y39" s="101"/>
+      <c r="Z39" s="102"/>
     </row>
     <row r="40" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="41" t="s">
+      <c r="A40" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="93" t="s">
+      <c r="B40" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="95" t="s">
+      <c r="C40" s="93"/>
+      <c r="D40" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E40" s="96"/>
-      <c r="F40" s="95" t="s">
+      <c r="E40" s="95"/>
+      <c r="F40" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="96"/>
+      <c r="G40" s="95"/>
       <c r="H40" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I40" s="27" t="s">
+      <c r="I40" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J40" s="4" t="s">
@@ -5304,7 +5295,7 @@
       <c r="L40" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M40" s="32" t="s">
+      <c r="M40" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N40" s="14" t="s">
@@ -5334,33 +5325,33 @@
       <c r="V40" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W40" s="101" t="s">
+      <c r="W40" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X40" s="102"/>
-      <c r="Y40" s="102"/>
-      <c r="Z40" s="103"/>
+      <c r="X40" s="101"/>
+      <c r="Y40" s="101"/>
+      <c r="Z40" s="102"/>
     </row>
     <row r="41" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="41" t="s">
+      <c r="A41" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="94"/>
-      <c r="D41" s="95" t="s">
+      <c r="C41" s="93"/>
+      <c r="D41" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="96"/>
-      <c r="F41" s="95" t="s">
+      <c r="E41" s="95"/>
+      <c r="F41" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="96"/>
+      <c r="G41" s="95"/>
       <c r="H41" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I41" s="27" t="s">
+      <c r="I41" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J41" s="4" t="s">
@@ -5372,7 +5363,7 @@
       <c r="L41" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M41" s="32" t="s">
+      <c r="M41" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N41" s="14" t="s">
@@ -5402,33 +5393,33 @@
       <c r="V41" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W41" s="101" t="s">
+      <c r="W41" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X41" s="102"/>
-      <c r="Y41" s="102"/>
-      <c r="Z41" s="103"/>
+      <c r="X41" s="101"/>
+      <c r="Y41" s="101"/>
+      <c r="Z41" s="102"/>
     </row>
     <row r="42" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="41" t="s">
+      <c r="A42" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="93" t="s">
+      <c r="B42" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="94"/>
-      <c r="D42" s="95" t="s">
+      <c r="C42" s="93"/>
+      <c r="D42" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="96"/>
-      <c r="F42" s="95" t="s">
+      <c r="E42" s="95"/>
+      <c r="F42" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="96"/>
+      <c r="G42" s="95"/>
       <c r="H42" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I42" s="27" t="s">
+      <c r="I42" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J42" s="4" t="s">
@@ -5440,7 +5431,7 @@
       <c r="L42" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M42" s="32" t="s">
+      <c r="M42" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N42" s="14" t="s">
@@ -5470,33 +5461,33 @@
       <c r="V42" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W42" s="101" t="s">
+      <c r="W42" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X42" s="102"/>
-      <c r="Y42" s="102"/>
-      <c r="Z42" s="103"/>
+      <c r="X42" s="101"/>
+      <c r="Y42" s="101"/>
+      <c r="Z42" s="102"/>
     </row>
     <row r="43" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="41" t="s">
+      <c r="A43" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="93" t="s">
+      <c r="B43" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="94"/>
-      <c r="D43" s="95" t="s">
+      <c r="C43" s="93"/>
+      <c r="D43" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="96"/>
-      <c r="F43" s="95" t="s">
+      <c r="E43" s="95"/>
+      <c r="F43" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G43" s="96"/>
+      <c r="G43" s="95"/>
       <c r="H43" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I43" s="27" t="s">
+      <c r="I43" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J43" s="4" t="s">
@@ -5508,7 +5499,7 @@
       <c r="L43" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M43" s="32" t="s">
+      <c r="M43" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N43" s="14" t="s">
@@ -5538,33 +5529,33 @@
       <c r="V43" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W43" s="101" t="s">
+      <c r="W43" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X43" s="102"/>
-      <c r="Y43" s="102"/>
-      <c r="Z43" s="103"/>
+      <c r="X43" s="101"/>
+      <c r="Y43" s="101"/>
+      <c r="Z43" s="102"/>
     </row>
     <row r="44" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="41" t="s">
+      <c r="A44" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="93" t="s">
+      <c r="B44" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="95" t="s">
+      <c r="C44" s="93"/>
+      <c r="D44" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="96"/>
-      <c r="F44" s="95" t="s">
+      <c r="E44" s="95"/>
+      <c r="F44" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="96"/>
+      <c r="G44" s="95"/>
       <c r="H44" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I44" s="27" t="s">
+      <c r="I44" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J44" s="4" t="s">
@@ -5576,7 +5567,7 @@
       <c r="L44" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M44" s="32" t="s">
+      <c r="M44" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N44" s="14" t="s">
@@ -5606,33 +5597,33 @@
       <c r="V44" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W44" s="101" t="s">
+      <c r="W44" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X44" s="102"/>
-      <c r="Y44" s="102"/>
-      <c r="Z44" s="103"/>
+      <c r="X44" s="101"/>
+      <c r="Y44" s="101"/>
+      <c r="Z44" s="102"/>
     </row>
     <row r="45" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="41" t="s">
+      <c r="A45" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="93" t="s">
+      <c r="B45" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="94"/>
-      <c r="D45" s="95" t="s">
+      <c r="C45" s="93"/>
+      <c r="D45" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="96"/>
-      <c r="F45" s="95" t="s">
+      <c r="E45" s="95"/>
+      <c r="F45" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G45" s="96"/>
+      <c r="G45" s="95"/>
       <c r="H45" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I45" s="27" t="s">
+      <c r="I45" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J45" s="4" t="s">
@@ -5644,7 +5635,7 @@
       <c r="L45" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M45" s="32" t="s">
+      <c r="M45" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N45" s="14" t="s">
@@ -5674,33 +5665,33 @@
       <c r="V45" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W45" s="101" t="s">
+      <c r="W45" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X45" s="102"/>
-      <c r="Y45" s="102"/>
-      <c r="Z45" s="103"/>
+      <c r="X45" s="101"/>
+      <c r="Y45" s="101"/>
+      <c r="Z45" s="102"/>
     </row>
     <row r="46" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="41" t="s">
+      <c r="A46" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="93" t="s">
+      <c r="B46" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="94"/>
-      <c r="D46" s="95" t="s">
+      <c r="C46" s="93"/>
+      <c r="D46" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="96"/>
-      <c r="F46" s="95" t="s">
+      <c r="E46" s="95"/>
+      <c r="F46" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G46" s="96"/>
+      <c r="G46" s="95"/>
       <c r="H46" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I46" s="27" t="s">
+      <c r="I46" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J46" s="4" t="s">
@@ -5712,7 +5703,7 @@
       <c r="L46" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M46" s="32" t="s">
+      <c r="M46" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N46" s="14" t="s">
@@ -5742,33 +5733,33 @@
       <c r="V46" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W46" s="101" t="s">
+      <c r="W46" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X46" s="102"/>
-      <c r="Y46" s="102"/>
-      <c r="Z46" s="103"/>
+      <c r="X46" s="101"/>
+      <c r="Y46" s="101"/>
+      <c r="Z46" s="102"/>
     </row>
     <row r="47" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="93" t="s">
+      <c r="B47" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="94"/>
-      <c r="D47" s="95" t="s">
+      <c r="C47" s="93"/>
+      <c r="D47" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="96"/>
-      <c r="F47" s="95" t="s">
+      <c r="E47" s="95"/>
+      <c r="F47" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G47" s="96"/>
+      <c r="G47" s="95"/>
       <c r="H47" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I47" s="27" t="s">
+      <c r="I47" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J47" s="4" t="s">
@@ -5780,7 +5771,7 @@
       <c r="L47" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M47" s="32" t="s">
+      <c r="M47" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N47" s="14" t="s">
@@ -5810,33 +5801,33 @@
       <c r="V47" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W47" s="101" t="s">
+      <c r="W47" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X47" s="102"/>
-      <c r="Y47" s="102"/>
-      <c r="Z47" s="103"/>
+      <c r="X47" s="101"/>
+      <c r="Y47" s="101"/>
+      <c r="Z47" s="102"/>
     </row>
     <row r="48" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="41" t="s">
+      <c r="A48" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="93" t="s">
+      <c r="B48" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="94"/>
-      <c r="D48" s="95" t="s">
+      <c r="C48" s="93"/>
+      <c r="D48" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="96"/>
-      <c r="F48" s="95" t="s">
+      <c r="E48" s="95"/>
+      <c r="F48" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G48" s="96"/>
+      <c r="G48" s="95"/>
       <c r="H48" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I48" s="27" t="s">
+      <c r="I48" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J48" s="4" t="s">
@@ -5848,7 +5839,7 @@
       <c r="L48" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M48" s="32" t="s">
+      <c r="M48" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N48" s="14" t="s">
@@ -5878,33 +5869,33 @@
       <c r="V48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W48" s="101" t="s">
+      <c r="W48" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X48" s="102"/>
-      <c r="Y48" s="102"/>
-      <c r="Z48" s="103"/>
+      <c r="X48" s="101"/>
+      <c r="Y48" s="101"/>
+      <c r="Z48" s="102"/>
     </row>
     <row r="49" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="41" t="s">
+      <c r="A49" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="93" t="s">
+      <c r="B49" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="94"/>
-      <c r="D49" s="95" t="s">
+      <c r="C49" s="93"/>
+      <c r="D49" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="E49" s="96"/>
-      <c r="F49" s="95" t="s">
+      <c r="E49" s="95"/>
+      <c r="F49" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="G49" s="96"/>
+      <c r="G49" s="95"/>
       <c r="H49" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="I49" s="27" t="s">
+      <c r="I49" s="26" t="s">
         <v>104</v>
       </c>
       <c r="J49" s="4" t="s">
@@ -5916,7 +5907,7 @@
       <c r="L49" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M49" s="32" t="s">
+      <c r="M49" s="30" t="s">
         <v>104</v>
       </c>
       <c r="N49" s="14" t="s">
@@ -5946,45 +5937,45 @@
       <c r="V49" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W49" s="101" t="s">
+      <c r="W49" s="100" t="s">
         <v>105</v>
       </c>
-      <c r="X49" s="102"/>
-      <c r="Y49" s="102"/>
-      <c r="Z49" s="103"/>
+      <c r="X49" s="101"/>
+      <c r="Y49" s="101"/>
+      <c r="Z49" s="102"/>
     </row>
     <row r="50" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="42" t="s">
+      <c r="A50" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="104" t="s">
+      <c r="B50" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="105"/>
-      <c r="D50" s="106" t="s">
+      <c r="C50" s="104"/>
+      <c r="D50" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="E50" s="107"/>
-      <c r="F50" s="106" t="s">
+      <c r="E50" s="106"/>
+      <c r="F50" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="G50" s="107"/>
-      <c r="H50" s="25" t="s">
+      <c r="G50" s="106"/>
+      <c r="H50" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="I50" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="J50" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="K50" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="L50" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="M50" s="35" t="s">
+      <c r="I50" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="J50" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="K50" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="L50" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="M50" s="33" t="s">
         <v>104</v>
       </c>
       <c r="N50" s="21" t="s">
@@ -6014,80 +6005,80 @@
       <c r="V50" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="W50" s="203" t="s">
+      <c r="W50" s="154" t="s">
         <v>105</v>
       </c>
-      <c r="X50" s="204"/>
-      <c r="Y50" s="204"/>
-      <c r="Z50" s="205"/>
+      <c r="X50" s="203"/>
+      <c r="Y50" s="203"/>
+      <c r="Z50" s="204"/>
     </row>
     <row r="51" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="108" t="s">
+      <c r="A51" s="107" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="109"/>
-      <c r="C51" s="109"/>
-      <c r="D51" s="109"/>
-      <c r="E51" s="110"/>
-      <c r="F51" s="116" t="s">
+      <c r="B51" s="108"/>
+      <c r="C51" s="108"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="109"/>
+      <c r="F51" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="G51" s="117"/>
-      <c r="H51" s="117"/>
-      <c r="I51" s="117"/>
-      <c r="J51" s="117"/>
-      <c r="K51" s="117"/>
-      <c r="L51" s="117"/>
-      <c r="M51" s="118"/>
-      <c r="N51" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="O51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="P51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="R51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="S51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="T51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="U51" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="V51" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="W51" s="206"/>
-      <c r="X51" s="207"/>
-      <c r="Y51" s="207"/>
-      <c r="Z51" s="208"/>
+      <c r="G51" s="116"/>
+      <c r="H51" s="116"/>
+      <c r="I51" s="116"/>
+      <c r="J51" s="116"/>
+      <c r="K51" s="116"/>
+      <c r="L51" s="116"/>
+      <c r="M51" s="117"/>
+      <c r="N51" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="O51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="P51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="R51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="S51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="T51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="U51" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="V51" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="W51" s="205"/>
+      <c r="X51" s="206"/>
+      <c r="Y51" s="206"/>
+      <c r="Z51" s="207"/>
     </row>
     <row r="52" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="111"/>
-      <c r="B52" s="112"/>
-      <c r="C52" s="112"/>
-      <c r="D52" s="112"/>
-      <c r="E52" s="113"/>
-      <c r="F52" s="119" t="s">
+      <c r="A52" s="110"/>
+      <c r="B52" s="111"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="112"/>
+      <c r="F52" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="G52" s="120"/>
-      <c r="H52" s="120"/>
-      <c r="I52" s="120"/>
-      <c r="J52" s="120"/>
-      <c r="K52" s="120"/>
-      <c r="L52" s="120"/>
-      <c r="M52" s="121"/>
-      <c r="N52" s="27" t="s">
+      <c r="G52" s="119"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="119"/>
+      <c r="J52" s="119"/>
+      <c r="K52" s="119"/>
+      <c r="L52" s="119"/>
+      <c r="M52" s="120"/>
+      <c r="N52" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O52" s="4" t="s">
@@ -6111,31 +6102,31 @@
       <c r="U52" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="V52" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="W52" s="209"/>
-      <c r="X52" s="210"/>
-      <c r="Y52" s="210"/>
-      <c r="Z52" s="211"/>
+      <c r="V52" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="W52" s="208"/>
+      <c r="X52" s="209"/>
+      <c r="Y52" s="209"/>
+      <c r="Z52" s="210"/>
     </row>
     <row r="53" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="111"/>
-      <c r="B53" s="112"/>
-      <c r="C53" s="112"/>
-      <c r="D53" s="112"/>
-      <c r="E53" s="113"/>
-      <c r="F53" s="119" t="s">
+      <c r="A53" s="110"/>
+      <c r="B53" s="111"/>
+      <c r="C53" s="111"/>
+      <c r="D53" s="111"/>
+      <c r="E53" s="112"/>
+      <c r="F53" s="118" t="s">
         <v>63</v>
       </c>
-      <c r="G53" s="120"/>
-      <c r="H53" s="120"/>
-      <c r="I53" s="120"/>
-      <c r="J53" s="120"/>
-      <c r="K53" s="120"/>
-      <c r="L53" s="120"/>
-      <c r="M53" s="121"/>
-      <c r="N53" s="27" t="s">
+      <c r="G53" s="119"/>
+      <c r="H53" s="119"/>
+      <c r="I53" s="119"/>
+      <c r="J53" s="119"/>
+      <c r="K53" s="119"/>
+      <c r="L53" s="119"/>
+      <c r="M53" s="120"/>
+      <c r="N53" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O53" s="4" t="s">
@@ -6159,31 +6150,31 @@
       <c r="U53" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="V53" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="W53" s="209"/>
-      <c r="X53" s="210"/>
-      <c r="Y53" s="210"/>
-      <c r="Z53" s="211"/>
+      <c r="V53" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="W53" s="208"/>
+      <c r="X53" s="209"/>
+      <c r="Y53" s="209"/>
+      <c r="Z53" s="210"/>
     </row>
     <row r="54" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="111"/>
-      <c r="B54" s="112"/>
-      <c r="C54" s="112"/>
-      <c r="D54" s="112"/>
-      <c r="E54" s="113"/>
-      <c r="F54" s="119" t="s">
+      <c r="A54" s="110"/>
+      <c r="B54" s="111"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="112"/>
+      <c r="F54" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="G54" s="120"/>
-      <c r="H54" s="120"/>
-      <c r="I54" s="120"/>
-      <c r="J54" s="120"/>
-      <c r="K54" s="120"/>
-      <c r="L54" s="120"/>
-      <c r="M54" s="121"/>
-      <c r="N54" s="27" t="s">
+      <c r="G54" s="119"/>
+      <c r="H54" s="119"/>
+      <c r="I54" s="119"/>
+      <c r="J54" s="119"/>
+      <c r="K54" s="119"/>
+      <c r="L54" s="119"/>
+      <c r="M54" s="120"/>
+      <c r="N54" s="26" t="s">
         <v>104</v>
       </c>
       <c r="O54" s="4" t="s">
@@ -6207,512 +6198,512 @@
       <c r="U54" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="V54" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="W54" s="209"/>
-      <c r="X54" s="210"/>
-      <c r="Y54" s="210"/>
-      <c r="Z54" s="211"/>
+      <c r="V54" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="W54" s="208"/>
+      <c r="X54" s="209"/>
+      <c r="Y54" s="209"/>
+      <c r="Z54" s="210"/>
     </row>
     <row r="55" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="114"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="115"/>
-      <c r="F55" s="133" t="s">
+      <c r="A55" s="113"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="114"/>
+      <c r="F55" s="130" t="s">
         <v>65</v>
       </c>
-      <c r="G55" s="134"/>
-      <c r="H55" s="134"/>
-      <c r="I55" s="134"/>
-      <c r="J55" s="134"/>
-      <c r="K55" s="134"/>
-      <c r="L55" s="134"/>
-      <c r="M55" s="135"/>
-      <c r="N55" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="O55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="P55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="R55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="S55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="T55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="U55" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="V55" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="W55" s="212"/>
-      <c r="X55" s="213"/>
-      <c r="Y55" s="213"/>
-      <c r="Z55" s="214"/>
+      <c r="G55" s="131"/>
+      <c r="H55" s="131"/>
+      <c r="I55" s="131"/>
+      <c r="J55" s="131"/>
+      <c r="K55" s="131"/>
+      <c r="L55" s="131"/>
+      <c r="M55" s="132"/>
+      <c r="N55" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="O55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="P55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="R55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="S55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="T55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="U55" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="V55" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="W55" s="211"/>
+      <c r="X55" s="212"/>
+      <c r="Y55" s="212"/>
+      <c r="Z55" s="213"/>
     </row>
     <row r="56" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="136" t="s">
+      <c r="A56" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="123"/>
-      <c r="C56" s="123"/>
-      <c r="D56" s="123"/>
-      <c r="E56" s="124"/>
-      <c r="F56" s="137" t="s">
+      <c r="B56" s="122"/>
+      <c r="C56" s="122"/>
+      <c r="D56" s="122"/>
+      <c r="E56" s="123"/>
+      <c r="F56" s="134" t="s">
         <v>75</v>
       </c>
-      <c r="G56" s="138"/>
-      <c r="H56" s="141" t="s">
+      <c r="G56" s="135"/>
+      <c r="H56" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="I56" s="143" t="s">
+      <c r="I56" s="140" t="s">
         <v>76</v>
       </c>
-      <c r="J56" s="144"/>
-      <c r="K56" s="144"/>
-      <c r="L56" s="144"/>
-      <c r="M56" s="144"/>
-      <c r="N56" s="144"/>
-      <c r="O56" s="145"/>
-      <c r="P56" s="116" t="s">
+      <c r="J56" s="141"/>
+      <c r="K56" s="141"/>
+      <c r="L56" s="141"/>
+      <c r="M56" s="141"/>
+      <c r="N56" s="141"/>
+      <c r="O56" s="142"/>
+      <c r="P56" s="115" t="s">
         <v>77</v>
       </c>
-      <c r="Q56" s="117"/>
-      <c r="R56" s="117"/>
-      <c r="S56" s="117"/>
-      <c r="T56" s="117"/>
-      <c r="U56" s="117"/>
-      <c r="V56" s="117"/>
-      <c r="W56" s="117"/>
-      <c r="X56" s="117"/>
-      <c r="Y56" s="117"/>
-      <c r="Z56" s="118"/>
+      <c r="Q56" s="116"/>
+      <c r="R56" s="116"/>
+      <c r="S56" s="116"/>
+      <c r="T56" s="116"/>
+      <c r="U56" s="116"/>
+      <c r="V56" s="116"/>
+      <c r="W56" s="116"/>
+      <c r="X56" s="116"/>
+      <c r="Y56" s="116"/>
+      <c r="Z56" s="117"/>
     </row>
     <row r="57" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="26" t="s">
+      <c r="A57" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="122" t="s">
+      <c r="B57" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="123"/>
-      <c r="D57" s="123"/>
-      <c r="E57" s="124"/>
-      <c r="F57" s="139"/>
-      <c r="G57" s="140"/>
-      <c r="H57" s="142"/>
-      <c r="I57" s="146"/>
-      <c r="J57" s="147"/>
-      <c r="K57" s="147"/>
-      <c r="L57" s="147"/>
-      <c r="M57" s="147"/>
-      <c r="N57" s="147"/>
-      <c r="O57" s="148"/>
-      <c r="P57" s="119" t="s">
+      <c r="C57" s="122"/>
+      <c r="D57" s="122"/>
+      <c r="E57" s="123"/>
+      <c r="F57" s="136"/>
+      <c r="G57" s="137"/>
+      <c r="H57" s="139"/>
+      <c r="I57" s="143"/>
+      <c r="J57" s="144"/>
+      <c r="K57" s="144"/>
+      <c r="L57" s="144"/>
+      <c r="M57" s="144"/>
+      <c r="N57" s="144"/>
+      <c r="O57" s="145"/>
+      <c r="P57" s="118" t="s">
         <v>78</v>
       </c>
-      <c r="Q57" s="120"/>
-      <c r="R57" s="120"/>
-      <c r="S57" s="120"/>
-      <c r="T57" s="120"/>
-      <c r="U57" s="120"/>
-      <c r="V57" s="120"/>
-      <c r="W57" s="120"/>
-      <c r="X57" s="120"/>
-      <c r="Y57" s="120"/>
-      <c r="Z57" s="121"/>
+      <c r="Q57" s="119"/>
+      <c r="R57" s="119"/>
+      <c r="S57" s="119"/>
+      <c r="T57" s="119"/>
+      <c r="U57" s="119"/>
+      <c r="V57" s="119"/>
+      <c r="W57" s="119"/>
+      <c r="X57" s="119"/>
+      <c r="Y57" s="119"/>
+      <c r="Z57" s="120"/>
     </row>
     <row r="58" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="95" t="s">
+      <c r="C58" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="102"/>
-      <c r="E58" s="103"/>
-      <c r="F58" s="125" t="s">
+      <c r="D58" s="101"/>
+      <c r="E58" s="102"/>
+      <c r="F58" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G58" s="126"/>
-      <c r="H58" s="24" t="s">
+      <c r="G58" s="95"/>
+      <c r="H58" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I58" s="127" t="s">
+      <c r="I58" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J58" s="128"/>
-      <c r="K58" s="128"/>
-      <c r="L58" s="128"/>
-      <c r="M58" s="128"/>
-      <c r="N58" s="128"/>
-      <c r="O58" s="129"/>
-      <c r="P58" s="130"/>
-      <c r="Q58" s="131"/>
-      <c r="R58" s="131"/>
-      <c r="S58" s="131"/>
-      <c r="T58" s="131"/>
-      <c r="U58" s="131"/>
-      <c r="V58" s="131"/>
-      <c r="W58" s="131"/>
-      <c r="X58" s="131"/>
-      <c r="Y58" s="131"/>
-      <c r="Z58" s="132"/>
+      <c r="J58" s="125"/>
+      <c r="K58" s="125"/>
+      <c r="L58" s="125"/>
+      <c r="M58" s="125"/>
+      <c r="N58" s="125"/>
+      <c r="O58" s="126"/>
+      <c r="P58" s="127"/>
+      <c r="Q58" s="128"/>
+      <c r="R58" s="128"/>
+      <c r="S58" s="128"/>
+      <c r="T58" s="128"/>
+      <c r="U58" s="128"/>
+      <c r="V58" s="128"/>
+      <c r="W58" s="128"/>
+      <c r="X58" s="128"/>
+      <c r="Y58" s="128"/>
+      <c r="Z58" s="129"/>
     </row>
     <row r="59" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="26" t="s">
         <v>1</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="95" t="s">
+      <c r="C59" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="102"/>
-      <c r="E59" s="103"/>
-      <c r="F59" s="125" t="s">
+      <c r="D59" s="101"/>
+      <c r="E59" s="102"/>
+      <c r="F59" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G59" s="126"/>
-      <c r="H59" s="24" t="s">
+      <c r="G59" s="95"/>
+      <c r="H59" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I59" s="127" t="s">
+      <c r="I59" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J59" s="128"/>
-      <c r="K59" s="128"/>
-      <c r="L59" s="128"/>
-      <c r="M59" s="128"/>
-      <c r="N59" s="128"/>
-      <c r="O59" s="129"/>
-      <c r="P59" s="119" t="s">
+      <c r="J59" s="125"/>
+      <c r="K59" s="125"/>
+      <c r="L59" s="125"/>
+      <c r="M59" s="125"/>
+      <c r="N59" s="125"/>
+      <c r="O59" s="126"/>
+      <c r="P59" s="118" t="s">
         <v>79</v>
       </c>
-      <c r="Q59" s="120"/>
-      <c r="R59" s="120"/>
-      <c r="S59" s="120"/>
-      <c r="T59" s="120"/>
-      <c r="U59" s="120"/>
-      <c r="V59" s="120"/>
-      <c r="W59" s="120"/>
-      <c r="X59" s="120"/>
-      <c r="Y59" s="120"/>
-      <c r="Z59" s="121"/>
+      <c r="Q59" s="119"/>
+      <c r="R59" s="119"/>
+      <c r="S59" s="119"/>
+      <c r="T59" s="119"/>
+      <c r="U59" s="119"/>
+      <c r="V59" s="119"/>
+      <c r="W59" s="119"/>
+      <c r="X59" s="119"/>
+      <c r="Y59" s="119"/>
+      <c r="Z59" s="120"/>
     </row>
     <row r="60" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="27" t="s">
+      <c r="A60" s="26" t="s">
         <v>2</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="95" t="s">
+      <c r="C60" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D60" s="102"/>
-      <c r="E60" s="103"/>
-      <c r="F60" s="125" t="s">
+      <c r="D60" s="101"/>
+      <c r="E60" s="102"/>
+      <c r="F60" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G60" s="126"/>
-      <c r="H60" s="24" t="s">
+      <c r="G60" s="95"/>
+      <c r="H60" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I60" s="127" t="s">
+      <c r="I60" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J60" s="128"/>
-      <c r="K60" s="128"/>
-      <c r="L60" s="128"/>
-      <c r="M60" s="128"/>
-      <c r="N60" s="128"/>
-      <c r="O60" s="129"/>
-      <c r="P60" s="119"/>
-      <c r="Q60" s="120"/>
-      <c r="R60" s="120"/>
-      <c r="S60" s="120"/>
-      <c r="T60" s="120"/>
-      <c r="U60" s="120"/>
-      <c r="V60" s="120"/>
-      <c r="W60" s="120"/>
-      <c r="X60" s="120"/>
-      <c r="Y60" s="120"/>
-      <c r="Z60" s="121"/>
+      <c r="J60" s="125"/>
+      <c r="K60" s="125"/>
+      <c r="L60" s="125"/>
+      <c r="M60" s="125"/>
+      <c r="N60" s="125"/>
+      <c r="O60" s="126"/>
+      <c r="P60" s="118"/>
+      <c r="Q60" s="119"/>
+      <c r="R60" s="119"/>
+      <c r="S60" s="119"/>
+      <c r="T60" s="119"/>
+      <c r="U60" s="119"/>
+      <c r="V60" s="119"/>
+      <c r="W60" s="119"/>
+      <c r="X60" s="119"/>
+      <c r="Y60" s="119"/>
+      <c r="Z60" s="120"/>
     </row>
     <row r="61" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="26" t="s">
         <v>3</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C61" s="95" t="s">
+      <c r="C61" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D61" s="102"/>
-      <c r="E61" s="103"/>
-      <c r="F61" s="125" t="s">
+      <c r="D61" s="101"/>
+      <c r="E61" s="102"/>
+      <c r="F61" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G61" s="126"/>
-      <c r="H61" s="24" t="s">
+      <c r="G61" s="95"/>
+      <c r="H61" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I61" s="127" t="s">
+      <c r="I61" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J61" s="128"/>
-      <c r="K61" s="128"/>
-      <c r="L61" s="128"/>
-      <c r="M61" s="128"/>
-      <c r="N61" s="128"/>
-      <c r="O61" s="129"/>
-      <c r="P61" s="119" t="s">
+      <c r="J61" s="125"/>
+      <c r="K61" s="125"/>
+      <c r="L61" s="125"/>
+      <c r="M61" s="125"/>
+      <c r="N61" s="125"/>
+      <c r="O61" s="126"/>
+      <c r="P61" s="118" t="s">
         <v>80</v>
       </c>
-      <c r="Q61" s="120"/>
-      <c r="R61" s="120"/>
-      <c r="S61" s="120"/>
-      <c r="T61" s="120"/>
-      <c r="U61" s="120"/>
-      <c r="V61" s="120"/>
-      <c r="W61" s="120"/>
-      <c r="X61" s="120"/>
-      <c r="Y61" s="120"/>
-      <c r="Z61" s="121"/>
+      <c r="Q61" s="119"/>
+      <c r="R61" s="119"/>
+      <c r="S61" s="119"/>
+      <c r="T61" s="119"/>
+      <c r="U61" s="119"/>
+      <c r="V61" s="119"/>
+      <c r="W61" s="119"/>
+      <c r="X61" s="119"/>
+      <c r="Y61" s="119"/>
+      <c r="Z61" s="120"/>
     </row>
     <row r="62" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="27" t="s">
+      <c r="A62" s="26" t="s">
         <v>4</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C62" s="95" t="s">
+      <c r="C62" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D62" s="102"/>
-      <c r="E62" s="103"/>
-      <c r="F62" s="125" t="s">
+      <c r="D62" s="101"/>
+      <c r="E62" s="102"/>
+      <c r="F62" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G62" s="126"/>
-      <c r="H62" s="24" t="s">
+      <c r="G62" s="95"/>
+      <c r="H62" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I62" s="127" t="s">
+      <c r="I62" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J62" s="128"/>
-      <c r="K62" s="128"/>
-      <c r="L62" s="128"/>
-      <c r="M62" s="128"/>
-      <c r="N62" s="128"/>
-      <c r="O62" s="129"/>
-      <c r="P62" s="149"/>
-      <c r="Q62" s="150"/>
-      <c r="R62" s="150"/>
-      <c r="S62" s="150"/>
-      <c r="T62" s="150"/>
-      <c r="U62" s="150"/>
-      <c r="V62" s="150"/>
-      <c r="W62" s="150"/>
-      <c r="X62" s="150"/>
-      <c r="Y62" s="150"/>
-      <c r="Z62" s="151"/>
+      <c r="J62" s="125"/>
+      <c r="K62" s="125"/>
+      <c r="L62" s="125"/>
+      <c r="M62" s="125"/>
+      <c r="N62" s="125"/>
+      <c r="O62" s="126"/>
+      <c r="P62" s="146"/>
+      <c r="Q62" s="147"/>
+      <c r="R62" s="147"/>
+      <c r="S62" s="147"/>
+      <c r="T62" s="147"/>
+      <c r="U62" s="147"/>
+      <c r="V62" s="147"/>
+      <c r="W62" s="147"/>
+      <c r="X62" s="147"/>
+      <c r="Y62" s="147"/>
+      <c r="Z62" s="148"/>
     </row>
     <row r="63" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="27" t="s">
+      <c r="A63" s="26" t="s">
         <v>5</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="95" t="s">
+      <c r="C63" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="102"/>
-      <c r="E63" s="103"/>
-      <c r="F63" s="125" t="s">
+      <c r="D63" s="101"/>
+      <c r="E63" s="102"/>
+      <c r="F63" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G63" s="126"/>
-      <c r="H63" s="24" t="s">
+      <c r="G63" s="95"/>
+      <c r="H63" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I63" s="127" t="s">
+      <c r="I63" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J63" s="128"/>
-      <c r="K63" s="128"/>
-      <c r="L63" s="128"/>
-      <c r="M63" s="128"/>
-      <c r="N63" s="128"/>
-      <c r="O63" s="129"/>
-      <c r="P63" s="119" t="s">
+      <c r="J63" s="125"/>
+      <c r="K63" s="125"/>
+      <c r="L63" s="125"/>
+      <c r="M63" s="125"/>
+      <c r="N63" s="125"/>
+      <c r="O63" s="126"/>
+      <c r="P63" s="118" t="s">
         <v>81</v>
       </c>
-      <c r="Q63" s="120"/>
-      <c r="R63" s="120"/>
-      <c r="S63" s="120"/>
-      <c r="T63" s="120"/>
-      <c r="U63" s="120"/>
-      <c r="V63" s="120"/>
-      <c r="W63" s="120"/>
-      <c r="X63" s="120"/>
-      <c r="Y63" s="120"/>
-      <c r="Z63" s="121"/>
+      <c r="Q63" s="119"/>
+      <c r="R63" s="119"/>
+      <c r="S63" s="119"/>
+      <c r="T63" s="119"/>
+      <c r="U63" s="119"/>
+      <c r="V63" s="119"/>
+      <c r="W63" s="119"/>
+      <c r="X63" s="119"/>
+      <c r="Y63" s="119"/>
+      <c r="Z63" s="120"/>
     </row>
     <row r="64" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="26" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C64" s="95" t="s">
+      <c r="C64" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D64" s="102"/>
-      <c r="E64" s="103"/>
-      <c r="F64" s="125" t="s">
+      <c r="D64" s="101"/>
+      <c r="E64" s="102"/>
+      <c r="F64" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G64" s="126"/>
-      <c r="H64" s="24" t="s">
+      <c r="G64" s="95"/>
+      <c r="H64" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I64" s="127" t="s">
+      <c r="I64" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J64" s="128"/>
-      <c r="K64" s="128"/>
-      <c r="L64" s="128"/>
-      <c r="M64" s="128"/>
-      <c r="N64" s="128"/>
-      <c r="O64" s="129"/>
-      <c r="P64" s="167"/>
-      <c r="Q64" s="48"/>
-      <c r="R64" s="48"/>
-      <c r="S64" s="48"/>
-      <c r="T64" s="48"/>
-      <c r="U64" s="48"/>
-      <c r="V64" s="48"/>
-      <c r="W64" s="48"/>
-      <c r="X64" s="48"/>
-      <c r="Y64" s="48"/>
-      <c r="Z64" s="168"/>
+      <c r="J64" s="125"/>
+      <c r="K64" s="125"/>
+      <c r="L64" s="125"/>
+      <c r="M64" s="125"/>
+      <c r="N64" s="125"/>
+      <c r="O64" s="126"/>
+      <c r="P64" s="164"/>
+      <c r="Q64" s="47"/>
+      <c r="R64" s="47"/>
+      <c r="S64" s="47"/>
+      <c r="T64" s="47"/>
+      <c r="U64" s="47"/>
+      <c r="V64" s="47"/>
+      <c r="W64" s="47"/>
+      <c r="X64" s="47"/>
+      <c r="Y64" s="47"/>
+      <c r="Z64" s="165"/>
     </row>
     <row r="65" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="27" t="s">
+      <c r="A65" s="26" t="s">
         <v>7</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="95" t="s">
+      <c r="C65" s="94" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="102"/>
-      <c r="E65" s="103"/>
-      <c r="F65" s="125" t="s">
+      <c r="D65" s="101"/>
+      <c r="E65" s="102"/>
+      <c r="F65" s="100" t="s">
         <v>102</v>
       </c>
-      <c r="G65" s="126"/>
-      <c r="H65" s="24" t="s">
+      <c r="G65" s="95"/>
+      <c r="H65" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I65" s="127" t="s">
+      <c r="I65" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="J65" s="128"/>
-      <c r="K65" s="128"/>
-      <c r="L65" s="128"/>
-      <c r="M65" s="128"/>
-      <c r="N65" s="128"/>
-      <c r="O65" s="129"/>
-      <c r="P65" s="130" t="s">
+      <c r="J65" s="125"/>
+      <c r="K65" s="125"/>
+      <c r="L65" s="125"/>
+      <c r="M65" s="125"/>
+      <c r="N65" s="125"/>
+      <c r="O65" s="126"/>
+      <c r="P65" s="127" t="s">
         <v>82</v>
       </c>
-      <c r="Q65" s="131"/>
-      <c r="R65" s="131"/>
-      <c r="S65" s="131"/>
-      <c r="T65" s="131"/>
-      <c r="U65" s="131"/>
-      <c r="V65" s="131"/>
-      <c r="W65" s="152"/>
-      <c r="X65" s="153" t="s">
+      <c r="Q65" s="128"/>
+      <c r="R65" s="128"/>
+      <c r="S65" s="128"/>
+      <c r="T65" s="128"/>
+      <c r="U65" s="128"/>
+      <c r="V65" s="128"/>
+      <c r="W65" s="149"/>
+      <c r="X65" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="Y65" s="131"/>
-      <c r="Z65" s="132"/>
+      <c r="Y65" s="128"/>
+      <c r="Z65" s="129"/>
     </row>
     <row r="66" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="27" t="s">
+      <c r="A66" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="154" t="s">
+      <c r="C66" s="151" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="155"/>
-      <c r="E66" s="156"/>
-      <c r="F66" s="157" t="s">
+      <c r="D66" s="152"/>
+      <c r="E66" s="153"/>
+      <c r="F66" s="154" t="s">
         <v>102</v>
       </c>
-      <c r="G66" s="158"/>
-      <c r="H66" s="28" t="s">
+      <c r="G66" s="155"/>
+      <c r="H66" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="I66" s="159" t="s">
+      <c r="I66" s="156" t="s">
         <v>108</v>
       </c>
-      <c r="J66" s="160"/>
-      <c r="K66" s="160"/>
-      <c r="L66" s="160"/>
-      <c r="M66" s="160"/>
-      <c r="N66" s="160"/>
-      <c r="O66" s="161"/>
-      <c r="P66" s="162"/>
-      <c r="Q66" s="163"/>
-      <c r="R66" s="163"/>
-      <c r="S66" s="163"/>
-      <c r="T66" s="163"/>
-      <c r="U66" s="163"/>
-      <c r="V66" s="163"/>
-      <c r="W66" s="164"/>
-      <c r="X66" s="165"/>
-      <c r="Y66" s="163"/>
-      <c r="Z66" s="166"/>
+      <c r="J66" s="157"/>
+      <c r="K66" s="157"/>
+      <c r="L66" s="157"/>
+      <c r="M66" s="157"/>
+      <c r="N66" s="157"/>
+      <c r="O66" s="158"/>
+      <c r="P66" s="159"/>
+      <c r="Q66" s="160"/>
+      <c r="R66" s="160"/>
+      <c r="S66" s="160"/>
+      <c r="T66" s="160"/>
+      <c r="U66" s="160"/>
+      <c r="V66" s="160"/>
+      <c r="W66" s="161"/>
+      <c r="X66" s="162"/>
+      <c r="Y66" s="160"/>
+      <c r="Z66" s="163"/>
     </row>
     <row r="67" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="136" t="s">
+      <c r="A67" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="123"/>
-      <c r="C67" s="123"/>
-      <c r="D67" s="123"/>
-      <c r="E67" s="124"/>
+      <c r="B67" s="122"/>
+      <c r="C67" s="122"/>
+      <c r="D67" s="122"/>
+      <c r="E67" s="123"/>
       <c r="F67" s="189">
         <v>0</v>
       </c>
@@ -6738,14 +6729,14 @@
       <c r="Z67" s="191"/>
     </row>
     <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="183" t="s">
+      <c r="A68" s="181" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="184"/>
-      <c r="C68" s="184"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="185"/>
-      <c r="F68" s="137" t="s">
+      <c r="B68" s="182"/>
+      <c r="C68" s="182"/>
+      <c r="D68" s="182"/>
+      <c r="E68" s="183"/>
+      <c r="F68" s="134" t="s">
         <v>74</v>
       </c>
       <c r="G68" s="192"/>
@@ -6774,25 +6765,25 @@
       <c r="Z68" s="200"/>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A69" s="183" t="s">
+      <c r="A69" s="181" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="184"/>
-      <c r="C69" s="184"/>
-      <c r="D69" s="184"/>
-      <c r="E69" s="185"/>
+      <c r="B69" s="182"/>
+      <c r="C69" s="182"/>
+      <c r="D69" s="182"/>
+      <c r="E69" s="183"/>
       <c r="F69" s="193"/>
       <c r="G69" s="194"/>
-      <c r="H69" s="136" t="s">
+      <c r="H69" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="I69" s="123"/>
-      <c r="J69" s="123"/>
-      <c r="K69" s="123"/>
-      <c r="L69" s="123"/>
-      <c r="M69" s="123"/>
-      <c r="N69" s="123"/>
-      <c r="O69" s="124"/>
+      <c r="I69" s="122"/>
+      <c r="J69" s="122"/>
+      <c r="K69" s="122"/>
+      <c r="L69" s="122"/>
+      <c r="M69" s="122"/>
+      <c r="N69" s="122"/>
+      <c r="O69" s="123"/>
       <c r="P69" s="194"/>
       <c r="Q69" s="194"/>
       <c r="R69" s="194"/>
@@ -6806,23 +6797,23 @@
       <c r="Z69" s="201"/>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A70" s="183" t="s">
+      <c r="A70" s="181" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="184"/>
-      <c r="C70" s="184"/>
-      <c r="D70" s="184"/>
-      <c r="E70" s="185"/>
+      <c r="B70" s="182"/>
+      <c r="C70" s="182"/>
+      <c r="D70" s="182"/>
+      <c r="E70" s="183"/>
       <c r="F70" s="193"/>
       <c r="G70" s="194"/>
-      <c r="H70" s="136"/>
-      <c r="I70" s="123"/>
-      <c r="J70" s="123"/>
-      <c r="K70" s="123"/>
-      <c r="L70" s="123"/>
-      <c r="M70" s="123"/>
-      <c r="N70" s="123"/>
-      <c r="O70" s="124"/>
+      <c r="H70" s="133"/>
+      <c r="I70" s="122"/>
+      <c r="J70" s="122"/>
+      <c r="K70" s="122"/>
+      <c r="L70" s="122"/>
+      <c r="M70" s="122"/>
+      <c r="N70" s="122"/>
+      <c r="O70" s="123"/>
       <c r="P70" s="194"/>
       <c r="Q70" s="194"/>
       <c r="R70" s="194"/>
@@ -6836,23 +6827,23 @@
       <c r="Z70" s="201"/>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A71" s="125"/>
-      <c r="B71" s="227"/>
-      <c r="C71" s="227"/>
-      <c r="D71" s="227"/>
-      <c r="E71" s="228"/>
+      <c r="A71" s="178"/>
+      <c r="B71" s="179"/>
+      <c r="C71" s="179"/>
+      <c r="D71" s="179"/>
+      <c r="E71" s="180"/>
       <c r="F71" s="193"/>
       <c r="G71" s="194"/>
-      <c r="H71" s="136" t="s">
+      <c r="H71" s="133" t="s">
         <v>72</v>
       </c>
-      <c r="I71" s="123"/>
-      <c r="J71" s="123"/>
-      <c r="K71" s="123"/>
-      <c r="L71" s="123"/>
-      <c r="M71" s="123"/>
-      <c r="N71" s="123"/>
-      <c r="O71" s="124"/>
+      <c r="I71" s="122"/>
+      <c r="J71" s="122"/>
+      <c r="K71" s="122"/>
+      <c r="L71" s="122"/>
+      <c r="M71" s="122"/>
+      <c r="N71" s="122"/>
+      <c r="O71" s="123"/>
       <c r="P71" s="194"/>
       <c r="Q71" s="194"/>
       <c r="R71" s="194"/>
@@ -6866,23 +6857,23 @@
       <c r="Z71" s="201"/>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A72" s="183" t="s">
+      <c r="A72" s="181" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="184"/>
-      <c r="C72" s="184"/>
-      <c r="D72" s="184"/>
-      <c r="E72" s="185"/>
+      <c r="B72" s="182"/>
+      <c r="C72" s="182"/>
+      <c r="D72" s="182"/>
+      <c r="E72" s="183"/>
       <c r="F72" s="193"/>
       <c r="G72" s="194"/>
-      <c r="H72" s="136"/>
-      <c r="I72" s="123"/>
-      <c r="J72" s="123"/>
-      <c r="K72" s="123"/>
-      <c r="L72" s="123"/>
-      <c r="M72" s="123"/>
-      <c r="N72" s="123"/>
-      <c r="O72" s="124"/>
+      <c r="H72" s="133"/>
+      <c r="I72" s="122"/>
+      <c r="J72" s="122"/>
+      <c r="K72" s="122"/>
+      <c r="L72" s="122"/>
+      <c r="M72" s="122"/>
+      <c r="N72" s="122"/>
+      <c r="O72" s="123"/>
       <c r="P72" s="194"/>
       <c r="Q72" s="194"/>
       <c r="R72" s="194"/>
@@ -6896,11 +6887,11 @@
       <c r="Z72" s="201"/>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A73" s="181"/>
-      <c r="B73" s="61"/>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="182"/>
+      <c r="A73" s="184"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="185"/>
       <c r="F73" s="193"/>
       <c r="G73" s="194"/>
       <c r="H73" s="186" t="s">
@@ -6926,23 +6917,23 @@
       <c r="Z73" s="201"/>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A74" s="169" t="s">
+      <c r="A74" s="166" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="170"/>
-      <c r="C74" s="170"/>
-      <c r="D74" s="170"/>
-      <c r="E74" s="171"/>
+      <c r="B74" s="167"/>
+      <c r="C74" s="167"/>
+      <c r="D74" s="167"/>
+      <c r="E74" s="168"/>
       <c r="F74" s="193"/>
       <c r="G74" s="194"/>
-      <c r="H74" s="172"/>
-      <c r="I74" s="173"/>
-      <c r="J74" s="173"/>
-      <c r="K74" s="173"/>
-      <c r="L74" s="173"/>
-      <c r="M74" s="173"/>
-      <c r="N74" s="173"/>
-      <c r="O74" s="174"/>
+      <c r="H74" s="169"/>
+      <c r="I74" s="170"/>
+      <c r="J74" s="170"/>
+      <c r="K74" s="170"/>
+      <c r="L74" s="170"/>
+      <c r="M74" s="170"/>
+      <c r="N74" s="170"/>
+      <c r="O74" s="171"/>
       <c r="P74" s="194"/>
       <c r="Q74" s="194"/>
       <c r="R74" s="194"/>
@@ -6956,21 +6947,21 @@
       <c r="Z74" s="201"/>
     </row>
     <row r="75" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="175"/>
-      <c r="B75" s="176"/>
-      <c r="C75" s="176"/>
-      <c r="D75" s="176"/>
-      <c r="E75" s="177"/>
+      <c r="A75" s="172"/>
+      <c r="B75" s="173"/>
+      <c r="C75" s="173"/>
+      <c r="D75" s="173"/>
+      <c r="E75" s="174"/>
       <c r="F75" s="195"/>
       <c r="G75" s="196"/>
-      <c r="H75" s="178"/>
-      <c r="I75" s="179"/>
-      <c r="J75" s="179"/>
-      <c r="K75" s="179"/>
-      <c r="L75" s="179"/>
-      <c r="M75" s="179"/>
-      <c r="N75" s="179"/>
-      <c r="O75" s="180"/>
+      <c r="H75" s="175"/>
+      <c r="I75" s="176"/>
+      <c r="J75" s="176"/>
+      <c r="K75" s="176"/>
+      <c r="L75" s="176"/>
+      <c r="M75" s="176"/>
+      <c r="N75" s="176"/>
+      <c r="O75" s="177"/>
       <c r="P75" s="196"/>
       <c r="Q75" s="196"/>
       <c r="R75" s="196"/>

--- a/backend/templates/Resumen_1ro_2do.xlsx
+++ b/backend/templates/Resumen_1ro_2do.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JavierWorkSpace\BatallaProject\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12EB1E3-3118-450D-B474-2002884A828F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D8ED3-0FA1-4843-A81D-09DD61DB05A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{299BAFB4-AE58-4015-B36E-D7CD92F1B4DD}"/>
   </bookViews>
